--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_RMSEP.xlsx
@@ -214,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,13 +230,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -246,7 +239,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -254,58 +247,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -608,9 +580,8 @@
   <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -671,52 +642,52 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>291.56687292973152</v>
+        <v>287.33704720169249</v>
       </c>
       <c r="C2">
-        <v>323.82083519250682</v>
+        <v>323.49213912576198</v>
       </c>
       <c r="D2">
-        <v>295.72812845585833</v>
+        <v>295.04093307838559</v>
       </c>
       <c r="E2">
-        <v>288.781190912797</v>
-      </c>
-      <c r="F2">
-        <v>279.17594486829069</v>
+        <v>287.70529007381322</v>
+      </c>
+      <c r="F2" s="3">
+        <v>278.03377061857952</v>
       </c>
       <c r="G2">
-        <v>274.57315676179752</v>
-      </c>
-      <c r="H2">
-        <v>264.13158203586289</v>
+        <v>273.69458192963492</v>
+      </c>
+      <c r="H2" s="2">
+        <v>262.50860918474382</v>
       </c>
       <c r="I2">
-        <v>263.15765270481461</v>
+        <v>261.80208175012763</v>
       </c>
       <c r="J2">
-        <v>267.31819428581031</v>
+        <v>265.7992499779441</v>
       </c>
       <c r="K2">
-        <v>268.90278768894137</v>
+        <v>269.00795139527293</v>
       </c>
       <c r="L2">
-        <v>272.09240597358041</v>
+        <v>272.24428907605522</v>
       </c>
       <c r="M2">
-        <v>264.73982541184228</v>
+        <v>265.45717390083968</v>
       </c>
       <c r="N2">
-        <v>271.94279831390492</v>
+        <v>272.98967703649362</v>
       </c>
       <c r="O2">
-        <v>269.11240543314841</v>
+        <v>270.00632522751562</v>
       </c>
       <c r="P2">
-        <v>271.94733767943569</v>
+        <v>272.82327398254739</v>
       </c>
       <c r="Q2">
-        <v>267.85040174994538</v>
+        <v>268.34106624489777</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -724,52 +695,52 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>304.9699766125359</v>
+        <v>303.51840457796311</v>
       </c>
       <c r="C3">
-        <v>311.08061044599413</v>
+        <v>310.75110893808028</v>
       </c>
       <c r="D3">
-        <v>290.1518036639917</v>
+        <v>289.49288471354322</v>
       </c>
       <c r="E3">
-        <v>287.41358874601951</v>
+        <v>287.00148349428309</v>
       </c>
       <c r="F3">
-        <v>287.15126507489663</v>
+        <v>290.16559185892987</v>
       </c>
       <c r="G3">
-        <v>297.23802568938299</v>
+        <v>298.57095910458031</v>
       </c>
       <c r="H3">
-        <v>290.48623648801072</v>
+        <v>292.02034953161132</v>
       </c>
       <c r="I3">
-        <v>297.30373969562169</v>
+        <v>297.97019361070181</v>
       </c>
       <c r="J3">
-        <v>301.16688958322828</v>
+        <v>301.7162738914987</v>
       </c>
       <c r="K3">
-        <v>302.80395758991301</v>
+        <v>301.9477725547568</v>
       </c>
       <c r="L3">
-        <v>303.32880950720619</v>
+        <v>302.76287305081621</v>
       </c>
       <c r="M3">
-        <v>309.05640940522687</v>
+        <v>309.18167051190699</v>
       </c>
       <c r="N3">
-        <v>315.03848692995808</v>
+        <v>314.87215642520931</v>
       </c>
       <c r="O3">
-        <v>322.96208742898659</v>
+        <v>322.87916939798919</v>
       </c>
       <c r="P3">
-        <v>332.85414940412699</v>
+        <v>331.1174112088612</v>
       </c>
       <c r="Q3">
-        <v>336.44557570432261</v>
+        <v>334.38174165678521</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -777,52 +748,52 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>326.70115683606201</v>
+        <v>329.44532436495979</v>
       </c>
       <c r="C4">
-        <v>319.58483521442162</v>
+        <v>320.13040897203012</v>
       </c>
       <c r="D4">
-        <v>298.63571803456722</v>
+        <v>299.83486512456841</v>
       </c>
       <c r="E4">
-        <v>296.14884772711758</v>
+        <v>297.01639211765348</v>
       </c>
       <c r="F4">
-        <v>299.39795467035219</v>
+        <v>301.27445015451411</v>
       </c>
       <c r="G4">
-        <v>295.26698090432092</v>
+        <v>297.00809399430489</v>
       </c>
       <c r="H4">
-        <v>296.21741723471132</v>
+        <v>299.30024209962869</v>
       </c>
       <c r="I4">
-        <v>289.46387251901223</v>
+        <v>292.00406474996868</v>
       </c>
       <c r="J4">
-        <v>289.67672945163127</v>
+        <v>292.07024998400698</v>
       </c>
       <c r="K4">
-        <v>288.0472988916211</v>
+        <v>290.53213050608019</v>
       </c>
       <c r="L4">
-        <v>299.47471821156051</v>
+        <v>301.90150686793078</v>
       </c>
       <c r="M4">
-        <v>299.80250454244361</v>
+        <v>301.98018125749269</v>
       </c>
       <c r="N4">
-        <v>297.41878797393571</v>
+        <v>299.95045466729289</v>
       </c>
       <c r="O4">
-        <v>294.12839435499109</v>
+        <v>295.52702510131769</v>
       </c>
       <c r="P4">
-        <v>298.04288146396539</v>
+        <v>298.26731441115339</v>
       </c>
       <c r="Q4">
-        <v>305.16056923554692</v>
+        <v>305.90704744078511</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -830,52 +801,52 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>296.23609627613649</v>
+        <v>295.49909337505738</v>
       </c>
       <c r="C5">
-        <v>292.52757390470413</v>
+        <v>292.95100426237991</v>
       </c>
       <c r="D5">
-        <v>292.49756867236209</v>
+        <v>292.2259951221954</v>
       </c>
       <c r="E5">
-        <v>292.48870039789813</v>
+        <v>291.9022951352855</v>
       </c>
       <c r="F5">
-        <v>300.50864371012472</v>
+        <v>299.50345863504009</v>
       </c>
       <c r="G5">
-        <v>300.46601938855542</v>
+        <v>300.45067837178931</v>
       </c>
       <c r="H5">
-        <v>304.63950984280478</v>
+        <v>306.32613648356249</v>
       </c>
       <c r="I5">
-        <v>304.09908530589712</v>
+        <v>305.90242321321762</v>
       </c>
       <c r="J5">
-        <v>294.41272097827238</v>
+        <v>296.52888866687522</v>
       </c>
       <c r="K5">
-        <v>290.27654173720828</v>
+        <v>292.03207477908501</v>
       </c>
       <c r="L5">
-        <v>294.17258373757102</v>
+        <v>296.2385786228935</v>
       </c>
       <c r="M5">
-        <v>294.36960946385778</v>
+        <v>297.39049970221868</v>
       </c>
       <c r="N5">
-        <v>297.87222694233049</v>
+        <v>301.35806705288991</v>
       </c>
       <c r="O5">
-        <v>304.56726748503831</v>
+        <v>309.30653465299162</v>
       </c>
       <c r="P5">
-        <v>303.49660016690189</v>
+        <v>307.62167034418309</v>
       </c>
       <c r="Q5">
-        <v>306.76416238880489</v>
+        <v>312.26577305838839</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -883,52 +854,52 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>299.83727207931707</v>
+        <v>297.32790475229268</v>
       </c>
       <c r="C6">
-        <v>291.91566547588661</v>
+        <v>292.08123282486758</v>
       </c>
       <c r="D6">
-        <v>290.06431114513077</v>
+        <v>289.64562844346591</v>
       </c>
       <c r="E6">
-        <v>289.16714407154302</v>
+        <v>289.16728309470801</v>
       </c>
       <c r="F6">
-        <v>309.29556971458089</v>
+        <v>309.3246784246453</v>
       </c>
       <c r="G6">
-        <v>296.75961986869078</v>
+        <v>297.82011193629899</v>
       </c>
       <c r="H6">
-        <v>303.71481796541542</v>
+        <v>306.29851048921341</v>
       </c>
       <c r="I6">
-        <v>296.92869900371039</v>
+        <v>298.29543159167531</v>
       </c>
       <c r="J6">
-        <v>286.56493620619011</v>
+        <v>287.77905025589502</v>
       </c>
       <c r="K6">
-        <v>289.73678022970762</v>
+        <v>291.40494986579728</v>
       </c>
       <c r="L6">
-        <v>293.48358938617719</v>
+        <v>294.73771585789189</v>
       </c>
       <c r="M6">
-        <v>300.55917443740339</v>
+        <v>300.32974959215397</v>
       </c>
       <c r="N6">
-        <v>307.23647153741467</v>
+        <v>306.57776566388458</v>
       </c>
       <c r="O6">
-        <v>308.5055471072003</v>
+        <v>309.10366420858333</v>
       </c>
       <c r="P6">
-        <v>308.18593070524639</v>
+        <v>308.89900992580931</v>
       </c>
       <c r="Q6">
-        <v>300.91118814684143</v>
+        <v>301.73683086458152</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -936,52 +907,52 @@
         <v>22</v>
       </c>
       <c r="B7">
-        <v>286.28069231800959</v>
+        <v>284.36132164142538</v>
       </c>
       <c r="C7">
-        <v>320.48953287044861</v>
+        <v>319.95382054700258</v>
       </c>
       <c r="D7">
-        <v>296.41345522316482</v>
+        <v>295.51678589055513</v>
       </c>
       <c r="E7">
-        <v>283.53316081054157</v>
+        <v>282.26834370240152</v>
       </c>
       <c r="F7">
-        <v>274.74889801087909</v>
+        <v>273.87708484767251</v>
       </c>
       <c r="G7">
-        <v>270.77780146286648</v>
-      </c>
-      <c r="H7">
-        <v>263.2742658278205</v>
+        <v>270.70911064731638</v>
+      </c>
+      <c r="H7" s="2">
+        <v>263.60094432348222</v>
       </c>
       <c r="I7">
-        <v>268.82524966480707</v>
+        <v>270.74025065638989</v>
       </c>
       <c r="J7">
-        <v>262.74098379689491</v>
+        <v>264.42581098999312</v>
       </c>
       <c r="K7">
-        <v>262.05325763475849</v>
+        <v>262.77655621138132</v>
       </c>
       <c r="L7">
-        <v>260.47831755422118</v>
+        <v>263.32617431363298</v>
       </c>
       <c r="M7">
-        <v>263.94053984155738</v>
+        <v>266.06058517356098</v>
       </c>
       <c r="N7">
-        <v>269.35287497773169</v>
+        <v>271.13981262181818</v>
       </c>
       <c r="O7">
-        <v>265.20935510362227</v>
+        <v>266.03952187321852</v>
       </c>
       <c r="P7">
-        <v>260.10886389744542</v>
+        <v>260.99005427139667</v>
       </c>
       <c r="Q7">
-        <v>262.05794860416978</v>
+        <v>263.83778104992211</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -989,52 +960,52 @@
         <v>23</v>
       </c>
       <c r="B8">
-        <v>317.58430395936358</v>
+        <v>317.28464655638339</v>
       </c>
       <c r="C8">
-        <v>310.80181097065127</v>
+        <v>310.31952178960569</v>
       </c>
       <c r="D8">
-        <v>300.75998110262458</v>
+        <v>300.11079595523063</v>
       </c>
       <c r="E8">
-        <v>299.76626547309138</v>
+        <v>299.80442536948959</v>
       </c>
       <c r="F8">
-        <v>295.56163690198201</v>
+        <v>295.95414785720811</v>
       </c>
       <c r="G8">
-        <v>283.81984989503582</v>
+        <v>283.44690690119131</v>
       </c>
       <c r="H8">
-        <v>290.62142386144262</v>
+        <v>290.49864891675378</v>
       </c>
       <c r="I8">
-        <v>282.74974031920641</v>
+        <v>281.83784902906109</v>
       </c>
       <c r="J8">
-        <v>279.10254490212827</v>
+        <v>278.83118377871978</v>
       </c>
       <c r="K8">
-        <v>282.8216463307084</v>
+        <v>284.01725371999089</v>
       </c>
       <c r="L8">
-        <v>285.18041912318029</v>
+        <v>286.17144986649259</v>
       </c>
       <c r="M8">
-        <v>288.39476526973692</v>
+        <v>288.0814905394576</v>
       </c>
       <c r="N8">
-        <v>286.40420674659032</v>
+        <v>285.67090457571891</v>
       </c>
       <c r="O8">
-        <v>284.03143859935727</v>
+        <v>284.0234166301135</v>
       </c>
       <c r="P8">
-        <v>284.14454163532929</v>
+        <v>284.46389570541862</v>
       </c>
       <c r="Q8">
-        <v>288.99909171221708</v>
+        <v>289.92629839113249</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1042,52 +1013,52 @@
         <v>24</v>
       </c>
       <c r="B9">
-        <v>315.66793013798082</v>
+        <v>317.82413238213309</v>
       </c>
       <c r="C9">
-        <v>310.49602626788959</v>
+        <v>310.80881203851573</v>
       </c>
       <c r="D9">
-        <v>300.29182305994101</v>
+        <v>300.99100489508572</v>
       </c>
       <c r="E9">
-        <v>300.00015081770113</v>
+        <v>300.62974722494732</v>
       </c>
       <c r="F9">
-        <v>296.05077304534791</v>
+        <v>296.63694537655812</v>
       </c>
       <c r="G9">
-        <v>284.4094536199907</v>
+        <v>285.58021096014522</v>
       </c>
       <c r="H9">
-        <v>290.33314978650537</v>
+        <v>292.08043798303532</v>
       </c>
       <c r="I9">
-        <v>281.83077627647191</v>
+        <v>283.62407928305697</v>
       </c>
       <c r="J9">
-        <v>277.73460052719912</v>
+        <v>279.60751572308681</v>
       </c>
       <c r="K9">
-        <v>282.80587225246552</v>
+        <v>283.53650680478478</v>
       </c>
       <c r="L9">
-        <v>287.0158833081075</v>
+        <v>287.75151835009649</v>
       </c>
       <c r="M9">
-        <v>290.26235833438068</v>
+        <v>290.11190838671678</v>
       </c>
       <c r="N9">
-        <v>289.4063356813553</v>
+        <v>289.73894712231572</v>
       </c>
       <c r="O9">
-        <v>285.24680898619692</v>
+        <v>285.66110265020501</v>
       </c>
       <c r="P9">
-        <v>279.01886867227671</v>
+        <v>278.63380132899158</v>
       </c>
       <c r="Q9">
-        <v>287.08177840048319</v>
+        <v>286.68175988601018</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -1095,52 +1066,52 @@
         <v>25</v>
       </c>
       <c r="B10">
-        <v>318.94566125108503</v>
+        <v>318.66092073540898</v>
       </c>
       <c r="C10">
-        <v>310.74084337305368</v>
+        <v>310.64397205785212</v>
       </c>
       <c r="D10">
-        <v>300.41636428366382</v>
+        <v>300.82708744914157</v>
       </c>
       <c r="E10">
-        <v>300.0857568490502</v>
+        <v>300.11553282308921</v>
       </c>
       <c r="F10">
-        <v>296.36935549208431</v>
+        <v>296.0279599860566</v>
       </c>
       <c r="G10">
-        <v>285.4803015602721</v>
+        <v>284.33044959398171</v>
       </c>
       <c r="H10">
-        <v>292.2923765927876</v>
+        <v>291.23920784650272</v>
       </c>
       <c r="I10">
-        <v>283.38483498749019</v>
+        <v>282.33149698661282</v>
       </c>
       <c r="J10">
-        <v>279.28924870619699</v>
+        <v>278.44605032377171</v>
       </c>
       <c r="K10">
-        <v>283.25099960579161</v>
+        <v>282.57066235286658</v>
       </c>
       <c r="L10">
-        <v>288.55946327095961</v>
+        <v>287.33894934694149</v>
       </c>
       <c r="M10">
-        <v>291.26793479796311</v>
+        <v>288.96360706764409</v>
       </c>
       <c r="N10">
-        <v>290.00111413012559</v>
+        <v>287.86690635678701</v>
       </c>
       <c r="O10">
-        <v>283.26574301825917</v>
+        <v>282.98790369749793</v>
       </c>
       <c r="P10">
-        <v>275.04456369157282</v>
+        <v>275.43587829761361</v>
       </c>
       <c r="Q10">
-        <v>282.46645828145842</v>
+        <v>282.15817522796141</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -1148,52 +1119,52 @@
         <v>26</v>
       </c>
       <c r="B11">
-        <v>316.11672471824232</v>
+        <v>317.9921477781445</v>
       </c>
       <c r="C11">
-        <v>310.80832128558279</v>
+        <v>311.02609905205691</v>
       </c>
       <c r="D11">
-        <v>301.12205555680021</v>
+        <v>300.51715691768641</v>
       </c>
       <c r="E11">
-        <v>300.44796574059978</v>
+        <v>298.80508695484639</v>
       </c>
       <c r="F11">
-        <v>296.49454812703698</v>
+        <v>294.6082693096738</v>
       </c>
       <c r="G11">
-        <v>285.63677042604832</v>
+        <v>285.4315610830779</v>
       </c>
       <c r="H11">
-        <v>291.91293195221868</v>
+        <v>290.67801997450732</v>
       </c>
       <c r="I11">
-        <v>284.10925917727599</v>
+        <v>282.85662064105622</v>
       </c>
       <c r="J11">
-        <v>279.73031837574518</v>
+        <v>280.09579265325158</v>
       </c>
       <c r="K11">
-        <v>283.62418887706968</v>
+        <v>283.50669530677368</v>
       </c>
       <c r="L11">
-        <v>287.11238667496218</v>
+        <v>288.6311648861664</v>
       </c>
       <c r="M11">
-        <v>288.10453544811389</v>
+        <v>291.21181624508381</v>
       </c>
       <c r="N11">
-        <v>285.99264223851452</v>
+        <v>290.00611945739399</v>
       </c>
       <c r="O11">
-        <v>282.40173567466599</v>
+        <v>287.62013054647088</v>
       </c>
       <c r="P11">
-        <v>278.92831704799619</v>
+        <v>284.26019845744861</v>
       </c>
       <c r="Q11">
-        <v>279.23060340480112</v>
+        <v>282.54439979336701</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1201,52 +1172,52 @@
         <v>27</v>
       </c>
       <c r="B12">
-        <v>295.31177401064531</v>
+        <v>298.47359362435338</v>
       </c>
       <c r="C12">
-        <v>290.41075753659521</v>
+        <v>291.40322332073129</v>
       </c>
       <c r="D12">
-        <v>289.79033454929771</v>
+        <v>290.89816277183093</v>
       </c>
       <c r="E12">
-        <v>290.66370399098929</v>
+        <v>291.58543190952111</v>
       </c>
       <c r="F12">
-        <v>300.74143711186451</v>
+        <v>301.67169445983308</v>
       </c>
       <c r="G12">
-        <v>296.66330843388653</v>
+        <v>298.80076592072078</v>
       </c>
       <c r="H12">
-        <v>293.02297990864258</v>
+        <v>296.52122230984293</v>
       </c>
       <c r="I12">
-        <v>289.30908048069767</v>
+        <v>292.03502829563843</v>
       </c>
       <c r="J12">
-        <v>277.58048626397391</v>
+        <v>279.93662986380059</v>
       </c>
       <c r="K12">
-        <v>276.64430656239517</v>
+        <v>278.30316404997421</v>
       </c>
       <c r="L12">
-        <v>275.66041904769611</v>
+        <v>276.99064565650121</v>
       </c>
       <c r="M12">
-        <v>283.94742617543432</v>
+        <v>284.84605850512958</v>
       </c>
       <c r="N12">
-        <v>283.08737883300569</v>
+        <v>285.49143060523983</v>
       </c>
       <c r="O12">
-        <v>290.79802182061098</v>
+        <v>292.89935656213498</v>
       </c>
       <c r="P12">
-        <v>291.99386428152201</v>
+        <v>294.09953080247948</v>
       </c>
       <c r="Q12">
-        <v>293.75803035517612</v>
+        <v>295.6657766222325</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1254,52 +1225,52 @@
         <v>28</v>
       </c>
       <c r="B13">
-        <v>293.90659008249469</v>
+        <v>293.75146902522027</v>
       </c>
       <c r="C13">
-        <v>291.07724433509333</v>
+        <v>290.48251922075201</v>
       </c>
       <c r="D13">
-        <v>285.62968902413769</v>
+        <v>285.81531810799743</v>
       </c>
       <c r="E13">
-        <v>283.53068208415021</v>
+        <v>283.99090754213353</v>
       </c>
       <c r="F13">
-        <v>286.18989783231478</v>
+        <v>286.16790534488399</v>
       </c>
       <c r="G13">
-        <v>297.5067028002527</v>
+        <v>297.61932910291608</v>
       </c>
       <c r="H13">
-        <v>300.10370252405261</v>
+        <v>301.01205214165049</v>
       </c>
       <c r="I13">
-        <v>297.59870650162009</v>
+        <v>298.86054685276588</v>
       </c>
       <c r="J13">
-        <v>291.64832275573838</v>
+        <v>292.65790405049648</v>
       </c>
       <c r="K13">
-        <v>289.99811891244809</v>
+        <v>292.28868947763181</v>
       </c>
       <c r="L13">
-        <v>289.23656825014552</v>
+        <v>291.93728388509658</v>
       </c>
       <c r="M13">
-        <v>288.01803878286091</v>
+        <v>290.69770960442008</v>
       </c>
       <c r="N13">
-        <v>290.31276200519437</v>
+        <v>293.30873768835181</v>
       </c>
       <c r="O13">
-        <v>293.41226783642742</v>
+        <v>296.34323825061227</v>
       </c>
       <c r="P13">
-        <v>296.30119509461332</v>
+        <v>299.12644732461598</v>
       </c>
       <c r="Q13">
-        <v>301.66318224977562</v>
+        <v>303.50471596735929</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1307,52 +1278,52 @@
         <v>29</v>
       </c>
       <c r="B14">
-        <v>288.8850900232863</v>
+        <v>285.19353525365858</v>
       </c>
       <c r="C14">
-        <v>320.2555474619511</v>
+        <v>320.24962396617838</v>
       </c>
       <c r="D14">
-        <v>295.98835953645408</v>
-      </c>
-      <c r="E14">
-        <v>282.95076144834547</v>
+        <v>295.84516436175687</v>
+      </c>
+      <c r="E14" s="2">
+        <v>282.61777551293972</v>
       </c>
       <c r="F14">
-        <v>274.52721770964263</v>
+        <v>274.72159347598688</v>
       </c>
       <c r="G14">
-        <v>271.07397341863901</v>
+        <v>271.36801955225229</v>
       </c>
       <c r="H14">
-        <v>265.08209881812081</v>
+        <v>264.3863524906767</v>
       </c>
       <c r="I14">
-        <v>270.07065417817358</v>
+        <v>269.3679168303654</v>
       </c>
       <c r="J14">
-        <v>264.91277375160541</v>
+        <v>264.85372261298858</v>
       </c>
       <c r="K14">
-        <v>264.45308581960398</v>
+        <v>264.58555840344599</v>
       </c>
       <c r="L14">
-        <v>265.10639170136221</v>
+        <v>263.98809296129178</v>
       </c>
       <c r="M14">
-        <v>270.99640415410221</v>
+        <v>269.76304440859138</v>
       </c>
       <c r="N14">
-        <v>278.71090797431498</v>
+        <v>277.86465972078281</v>
       </c>
       <c r="O14">
-        <v>273.08856789976812</v>
+        <v>272.54582868652841</v>
       </c>
       <c r="P14">
-        <v>265.24244156883498</v>
+        <v>264.09932826384778</v>
       </c>
       <c r="Q14">
-        <v>258.92203791856718</v>
+        <v>256.82599951005437</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1360,52 +1331,52 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <v>286.36880057170379</v>
+        <v>289.42694827808748</v>
       </c>
       <c r="C15">
-        <v>320.50716969860559</v>
+        <v>321.33837859449278</v>
       </c>
       <c r="D15">
-        <v>296.52789114756058</v>
-      </c>
-      <c r="E15">
-        <v>283.44768790215011</v>
+        <v>296.90673189484443</v>
+      </c>
+      <c r="E15" s="2">
+        <v>284.59345836634168</v>
       </c>
       <c r="F15">
-        <v>275.13471809347351</v>
+        <v>275.99955057675419</v>
       </c>
       <c r="G15">
-        <v>272.34488722405808</v>
+        <v>273.13987050971542</v>
       </c>
       <c r="H15">
-        <v>265.91786618046342</v>
+        <v>266.64933676631142</v>
       </c>
       <c r="I15">
-        <v>271.94498168405801</v>
+        <v>273.31509672492501</v>
       </c>
       <c r="J15">
-        <v>267.21170505847539</v>
+        <v>267.41060057504347</v>
       </c>
       <c r="K15">
-        <v>265.87296590619212</v>
+        <v>266.61837165706783</v>
       </c>
       <c r="L15">
-        <v>266.56659357751653</v>
+        <v>267.05655992910869</v>
       </c>
       <c r="M15">
-        <v>270.91648691068849</v>
+        <v>272.37274434124703</v>
       </c>
       <c r="N15">
-        <v>279.62079979491421</v>
+        <v>281.47077272855847</v>
       </c>
       <c r="O15">
-        <v>274.6109848920849</v>
+        <v>275.34331711131142</v>
       </c>
       <c r="P15">
-        <v>268.15689043758289</v>
+        <v>269.33180288918732</v>
       </c>
       <c r="Q15">
-        <v>260.91940295698367</v>
+        <v>261.95378939897449</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1413,52 +1384,52 @@
         <v>31</v>
       </c>
       <c r="B16">
-        <v>284.3992181894688</v>
+        <v>284.87212935285697</v>
       </c>
       <c r="C16">
-        <v>320.0890734299976</v>
-      </c>
-      <c r="D16">
-        <v>295.89327314157021</v>
-      </c>
-      <c r="E16">
-        <v>282.14136514241682</v>
+        <v>320.6700788479651</v>
+      </c>
+      <c r="D16" s="3">
+        <v>296.71093417139599</v>
+      </c>
+      <c r="E16" s="2">
+        <v>283.25058498058468</v>
       </c>
       <c r="F16">
-        <v>274.55530253197128</v>
+        <v>274.62792557388798</v>
       </c>
       <c r="G16">
-        <v>271.29365028011682</v>
+        <v>271.58345096092881</v>
       </c>
       <c r="H16">
-        <v>264.59156931535682</v>
+        <v>264.99045675105992</v>
       </c>
       <c r="I16">
-        <v>270.2275940550677</v>
+        <v>270.42501009500688</v>
       </c>
       <c r="J16">
-        <v>265.84882935232628</v>
+        <v>265.81937055818361</v>
       </c>
       <c r="K16">
-        <v>265.72418850727149</v>
+        <v>265.69687119935782</v>
       </c>
       <c r="L16">
-        <v>266.13120884802078</v>
+        <v>265.82085039634569</v>
       </c>
       <c r="M16">
-        <v>270.06628812675581</v>
+        <v>270.10486316774802</v>
       </c>
       <c r="N16">
-        <v>276.60990141614229</v>
+        <v>279.26676239886348</v>
       </c>
       <c r="O16">
-        <v>272.01180097943381</v>
+        <v>273.69066950908802</v>
       </c>
       <c r="P16">
-        <v>265.81333853373729</v>
+        <v>266.04731309215123</v>
       </c>
       <c r="Q16">
-        <v>258.74571273313751</v>
+        <v>260.38064732205652</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -1466,52 +1437,52 @@
         <v>32</v>
       </c>
       <c r="B17">
-        <v>285.68689172075028</v>
-      </c>
-      <c r="C17">
-        <v>320.083943188283</v>
+        <v>287.91687103370708</v>
+      </c>
+      <c r="C17" s="3">
+        <v>320.29260827717007</v>
       </c>
       <c r="D17">
-        <v>296.06131455716508</v>
-      </c>
-      <c r="E17">
-        <v>283.17348947807608</v>
+        <v>296.19612648439721</v>
+      </c>
+      <c r="E17" s="2">
+        <v>283.25468724465537</v>
       </c>
       <c r="F17">
-        <v>275.60287869292802</v>
+        <v>274.91498017256959</v>
       </c>
       <c r="G17">
-        <v>272.62736799289752</v>
+        <v>271.99151854243502</v>
       </c>
       <c r="H17">
-        <v>264.62159927563869</v>
+        <v>265.99725443962518</v>
       </c>
       <c r="I17">
-        <v>271.02992887558162</v>
+        <v>271.53819739374461</v>
       </c>
       <c r="J17">
-        <v>265.74200811811102</v>
+        <v>266.74436345854411</v>
       </c>
       <c r="K17">
-        <v>265.3444309627497</v>
+        <v>266.53970857894763</v>
       </c>
       <c r="L17">
-        <v>265.91941981230758</v>
+        <v>266.62500226213371</v>
       </c>
       <c r="M17">
-        <v>271.29497246109162</v>
+        <v>272.3952115208142</v>
       </c>
       <c r="N17">
-        <v>278.52681484148621</v>
+        <v>279.75533604520132</v>
       </c>
       <c r="O17">
-        <v>272.36778551547911</v>
+        <v>274.37278419489871</v>
       </c>
       <c r="P17">
-        <v>265.69189508289662</v>
+        <v>267.08052359564812</v>
       </c>
       <c r="Q17">
-        <v>258.88839358836458</v>
+        <v>260.96318365491408</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -1519,52 +1490,52 @@
         <v>33</v>
       </c>
       <c r="B18">
-        <v>299.93163848981618</v>
+        <v>300.66930679831893</v>
       </c>
       <c r="C18">
-        <v>290.43213924948941</v>
+        <v>290.24118453522289</v>
       </c>
       <c r="D18">
-        <v>289.25131636242241</v>
-      </c>
-      <c r="E18">
-        <v>289.84962195928688</v>
+        <v>290.01624890761309</v>
+      </c>
+      <c r="E18" s="3">
+        <v>291.01656607909479</v>
       </c>
       <c r="F18">
-        <v>297.49471635081591</v>
+        <v>299.3777909962152</v>
       </c>
       <c r="G18">
-        <v>290.61853061531872</v>
+        <v>292.7161720839602</v>
       </c>
       <c r="H18">
-        <v>298.26684991472189</v>
+        <v>298.93070149029779</v>
       </c>
       <c r="I18">
-        <v>283.89237775212268</v>
-      </c>
-      <c r="J18">
-        <v>272.71818153214741</v>
+        <v>287.00305756119332</v>
+      </c>
+      <c r="J18" s="2">
+        <v>275.21923897867009</v>
       </c>
       <c r="K18">
-        <v>265.92454450706748</v>
+        <v>267.83786286389858</v>
       </c>
       <c r="L18">
-        <v>262.35301215078852</v>
+        <v>264.03433953389401</v>
       </c>
       <c r="M18">
-        <v>264.18469837025151</v>
+        <v>265.92613220971492</v>
       </c>
       <c r="N18">
-        <v>263.70292731455538</v>
+        <v>266.05957389835493</v>
       </c>
       <c r="O18">
-        <v>268.65714881605908</v>
+        <v>271.54832944794038</v>
       </c>
       <c r="P18">
-        <v>269.79340710159698</v>
+        <v>273.38270605797089</v>
       </c>
       <c r="Q18">
-        <v>272.17428317125717</v>
+        <v>274.32569363865173</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1572,52 +1543,52 @@
         <v>34</v>
       </c>
       <c r="B19">
-        <v>298.57030911473271</v>
+        <v>299.51655894955991</v>
       </c>
       <c r="C19">
-        <v>290.56627023283272</v>
+        <v>290.32772587257932</v>
       </c>
       <c r="D19">
-        <v>288.19725250767658</v>
+        <v>287.84328747493453</v>
       </c>
       <c r="E19">
-        <v>287.85306940481797</v>
+        <v>287.16750311390467</v>
       </c>
       <c r="F19">
-        <v>309.11574468801842</v>
+        <v>309.26517973957249</v>
       </c>
       <c r="G19">
-        <v>296.20731368212478</v>
+        <v>298.21285864727008</v>
       </c>
       <c r="H19">
-        <v>291.59997748835139</v>
-      </c>
-      <c r="I19">
-        <v>271.40746906743442</v>
+        <v>292.97628942917669</v>
+      </c>
+      <c r="I19" s="2">
+        <v>272.99361685745532</v>
       </c>
       <c r="J19">
-        <v>270.3991021192125</v>
+        <v>271.53434501098718</v>
       </c>
       <c r="K19">
-        <v>260.00489547906551</v>
+        <v>261.23392615448108</v>
       </c>
       <c r="L19">
-        <v>258.32175021258098</v>
+        <v>259.68097803212862</v>
       </c>
       <c r="M19">
-        <v>263.75297222921171</v>
+        <v>264.95566394986002</v>
       </c>
       <c r="N19">
-        <v>265.54374062598703</v>
+        <v>266.56475567842352</v>
       </c>
       <c r="O19">
-        <v>265.69626982874928</v>
+        <v>265.01524019599412</v>
       </c>
       <c r="P19">
-        <v>266.45469891590972</v>
+        <v>266.03271880117882</v>
       </c>
       <c r="Q19">
-        <v>264.08293836077621</v>
+        <v>262.11198216217258</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1625,52 +1596,52 @@
         <v>35</v>
       </c>
       <c r="B20">
-        <v>296.11244226828018</v>
+        <v>300.52715482362328</v>
       </c>
       <c r="C20">
-        <v>290.60168742573512</v>
+        <v>291.04951406515278</v>
       </c>
       <c r="D20">
-        <v>288.54141808087508</v>
+        <v>288.8771819603171</v>
       </c>
       <c r="E20">
-        <v>288.28896949292039</v>
+        <v>288.69694004967869</v>
       </c>
       <c r="F20">
-        <v>292.83020463906922</v>
+        <v>293.8315717341477</v>
       </c>
       <c r="G20">
-        <v>295.67419328008879</v>
+        <v>298.72882980061519</v>
       </c>
       <c r="H20">
-        <v>290.70710016026823</v>
-      </c>
-      <c r="I20">
-        <v>274.30623055683992</v>
-      </c>
-      <c r="J20">
-        <v>260.88931559458757</v>
+        <v>293.69212839002472</v>
+      </c>
+      <c r="I20" s="2">
+        <v>277.28358630799659</v>
+      </c>
+      <c r="J20" s="3">
+        <v>264.47316546506818</v>
       </c>
       <c r="K20">
-        <v>252.97177145656099</v>
+        <v>257.46515351385779</v>
       </c>
       <c r="L20">
-        <v>258.91501732101813</v>
+        <v>262.97182738374062</v>
       </c>
       <c r="M20">
-        <v>261.80450772076972</v>
+        <v>267.44036187806648</v>
       </c>
       <c r="N20">
-        <v>265.50070670956342</v>
+        <v>270.91665730677607</v>
       </c>
       <c r="O20">
-        <v>267.45780186629992</v>
+        <v>271.38825549697822</v>
       </c>
       <c r="P20">
-        <v>262.40224038881121</v>
+        <v>264.08633398508641</v>
       </c>
       <c r="Q20">
-        <v>260.83940767558869</v>
+        <v>262.47079115285351</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -1678,52 +1649,52 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>301.07344211594278</v>
+        <v>301.86514057562181</v>
       </c>
       <c r="C21">
-        <v>310.9185018858243</v>
+        <v>310.79775624046732</v>
       </c>
       <c r="D21">
-        <v>290.12231319802908</v>
+        <v>290.15174418011418</v>
       </c>
       <c r="E21">
-        <v>286.82024479747849</v>
+        <v>286.16109427219169</v>
       </c>
       <c r="F21">
-        <v>283.95140512206967</v>
+        <v>283.49093644535247</v>
       </c>
       <c r="G21">
-        <v>292.27039002069353</v>
+        <v>290.41068721158871</v>
       </c>
       <c r="H21">
-        <v>288.06061608031138</v>
+        <v>285.48929277654179</v>
       </c>
       <c r="I21">
-        <v>297.46588733016148</v>
+        <v>294.30949975530842</v>
       </c>
       <c r="J21">
-        <v>297.41242563768748</v>
+        <v>292.89050304632673</v>
       </c>
       <c r="K21">
-        <v>295.849767240338</v>
+        <v>292.09838043710801</v>
       </c>
       <c r="L21">
-        <v>300.90519888969482</v>
+        <v>298.19742929427531</v>
       </c>
       <c r="M21">
-        <v>310.46179914972208</v>
+        <v>307.49687153681901</v>
       </c>
       <c r="N21">
-        <v>314.10620670835641</v>
+        <v>312.11493689727729</v>
       </c>
       <c r="O21">
-        <v>325.37786546933887</v>
+        <v>323.97342795284789</v>
       </c>
       <c r="P21">
-        <v>331.90096764825671</v>
+        <v>331.70229027341782</v>
       </c>
       <c r="Q21">
-        <v>334.6960313627784</v>
+        <v>335.07716254890443</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1731,52 +1702,52 @@
         <v>37</v>
       </c>
       <c r="B22">
-        <v>302.65860325790601</v>
+        <v>300.59787546283428</v>
       </c>
       <c r="C22">
-        <v>310.81043867575778</v>
+        <v>310.84257823947758</v>
       </c>
       <c r="D22">
-        <v>290.11967337435652</v>
+        <v>289.90685260928348</v>
       </c>
       <c r="E22">
-        <v>285.95321938556339</v>
+        <v>286.16310591950571</v>
       </c>
       <c r="F22">
-        <v>284.14447985369128</v>
+        <v>284.19249825067197</v>
       </c>
       <c r="G22">
-        <v>288.98004372623649</v>
+        <v>290.58342335041169</v>
       </c>
       <c r="H22">
-        <v>284.91751958213291</v>
+        <v>285.78917319077323</v>
       </c>
       <c r="I22">
-        <v>295.71144147309832</v>
+        <v>297.5055544100822</v>
       </c>
       <c r="J22">
-        <v>298.04506230474288</v>
+        <v>299.19019126529548</v>
       </c>
       <c r="K22">
-        <v>297.04984826399721</v>
+        <v>297.12398356638829</v>
       </c>
       <c r="L22">
-        <v>300.55928322309842</v>
+        <v>301.90126142905672</v>
       </c>
       <c r="M22">
-        <v>310.00845822552247</v>
+        <v>309.68118715595142</v>
       </c>
       <c r="N22">
-        <v>312.98371781687501</v>
+        <v>312.34943376596169</v>
       </c>
       <c r="O22">
-        <v>322.29806890701923</v>
+        <v>319.84730108257088</v>
       </c>
       <c r="P22">
-        <v>330.26229657390593</v>
+        <v>329.84174952960672</v>
       </c>
       <c r="Q22">
-        <v>332.12080963740237</v>
+        <v>332.17093161183448</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -1784,52 +1755,52 @@
         <v>38</v>
       </c>
       <c r="B23">
-        <v>295.09181082701548</v>
+        <v>294.13216213510191</v>
       </c>
       <c r="C23">
-        <v>290.55270229162301</v>
+        <v>290.20989894610068</v>
       </c>
       <c r="D23">
-        <v>309.36477114119481</v>
+        <v>309.77042660286168</v>
       </c>
       <c r="E23">
-        <v>299.12141403516932</v>
+        <v>299.98555016588728</v>
       </c>
       <c r="F23">
-        <v>288.70400649702088</v>
+        <v>289.98916429943932</v>
       </c>
       <c r="G23">
-        <v>288.6537011805429</v>
+        <v>289.4929695274526</v>
       </c>
       <c r="H23">
-        <v>286.55039617678551</v>
+        <v>285.88212422064811</v>
       </c>
       <c r="I23">
-        <v>292.84215507240822</v>
+        <v>291.30688527607663</v>
       </c>
       <c r="J23">
-        <v>294.49468845161061</v>
+        <v>293.94872711338257</v>
       </c>
       <c r="K23">
-        <v>303.34082939044998</v>
+        <v>302.48725463919089</v>
       </c>
       <c r="L23">
-        <v>307.82190009320823</v>
+        <v>307.28659474764521</v>
       </c>
       <c r="M23">
-        <v>313.59293906752742</v>
+        <v>313.07478972426088</v>
       </c>
       <c r="N23">
-        <v>312.05023421394588</v>
+        <v>312.10007512736388</v>
       </c>
       <c r="O23">
-        <v>314.072830651944</v>
+        <v>313.13319074358532</v>
       </c>
       <c r="P23">
-        <v>317.1418735917448</v>
+        <v>315.47138388854057</v>
       </c>
       <c r="Q23">
-        <v>323.24569083083639</v>
+        <v>321.07793352080279</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -1837,52 +1808,52 @@
         <v>39</v>
       </c>
       <c r="B24">
-        <v>367.12211511067051</v>
+        <v>367.59792616506019</v>
       </c>
       <c r="C24">
-        <v>367.12211511067051</v>
+        <v>367.59792616506019</v>
       </c>
       <c r="D24">
-        <v>390.63006617671209</v>
+        <v>391.77676727696388</v>
       </c>
       <c r="E24">
-        <v>393.250672682485</v>
+        <v>394.52008307189919</v>
       </c>
       <c r="F24">
-        <v>403.06654761290991</v>
+        <v>402.38011161327432</v>
       </c>
       <c r="G24">
-        <v>428.35164496165879</v>
+        <v>428.80647472231209</v>
       </c>
       <c r="H24">
-        <v>429.44325542221452</v>
+        <v>428.32830913642391</v>
       </c>
       <c r="I24">
-        <v>428.55312075799202</v>
+        <v>426.42352433446081</v>
       </c>
       <c r="J24">
-        <v>435.9817287792003</v>
+        <v>434.67041400449921</v>
       </c>
       <c r="K24">
-        <v>447.38950420166969</v>
+        <v>445.0125123703902</v>
       </c>
       <c r="L24">
-        <v>469.92711279575201</v>
+        <v>467.24101049290391</v>
       </c>
       <c r="M24">
-        <v>468.96178419155939</v>
+        <v>465.89456524795969</v>
       </c>
       <c r="N24">
-        <v>459.51169256217452</v>
+        <v>459.10687380298941</v>
       </c>
       <c r="O24">
-        <v>452.59567883198719</v>
+        <v>451.08287401146691</v>
       </c>
       <c r="P24">
-        <v>446.41770078360531</v>
+        <v>444.62814832464198</v>
       </c>
       <c r="Q24">
-        <v>445.00989981983162</v>
+        <v>442.5023476603144</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -1890,52 +1861,52 @@
         <v>40</v>
       </c>
       <c r="B25">
-        <v>370.71628680221829</v>
+        <v>370.49894939188442</v>
       </c>
       <c r="C25">
-        <v>370.71628680221829</v>
+        <v>370.49894939188442</v>
       </c>
       <c r="D25">
-        <v>391.39728165540453</v>
+        <v>391.03466075447938</v>
       </c>
       <c r="E25">
-        <v>400.26953165447611</v>
+        <v>399.58981612124381</v>
       </c>
       <c r="F25">
-        <v>427.23835504317799</v>
+        <v>426.7849697458762</v>
       </c>
       <c r="G25">
-        <v>428.44213417647501</v>
+        <v>428.32456905005267</v>
       </c>
       <c r="H25">
-        <v>444.14224137747863</v>
+        <v>444.57777571140628</v>
       </c>
       <c r="I25">
-        <v>473.04327887764452</v>
+        <v>474.77188425568409</v>
       </c>
       <c r="J25">
-        <v>487.20855062196478</v>
+        <v>488.75704931085409</v>
       </c>
       <c r="K25">
-        <v>478.42411639697667</v>
+        <v>480.16878126491957</v>
       </c>
       <c r="L25">
-        <v>483.51723014393201</v>
+        <v>485.56187382006698</v>
       </c>
       <c r="M25">
-        <v>490.44451045658309</v>
+        <v>493.98455341905441</v>
       </c>
       <c r="N25">
-        <v>503.36772576252031</v>
+        <v>507.58267278630319</v>
       </c>
       <c r="O25">
-        <v>513.92735741831802</v>
+        <v>518.53998400103228</v>
       </c>
       <c r="P25">
-        <v>510.29553972174261</v>
+        <v>513.37575230360426</v>
       </c>
       <c r="Q25">
-        <v>509.07636091377299</v>
+        <v>511.78490816538499</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -1943,52 +1914,52 @@
         <v>41</v>
       </c>
       <c r="B26">
-        <v>368.27741098309713</v>
+        <v>367.21660207750142</v>
       </c>
       <c r="C26">
-        <v>367.72224643157392</v>
+        <v>367.21660207750142</v>
       </c>
       <c r="D26">
-        <v>379.33504174821002</v>
+        <v>377.60322205778982</v>
       </c>
       <c r="E26">
-        <v>380.33841431146391</v>
+        <v>378.63186049748037</v>
       </c>
       <c r="F26">
-        <v>400.08028600727761</v>
+        <v>397.73686988504448</v>
       </c>
       <c r="G26">
-        <v>410.10951333905962</v>
+        <v>407.28812853023197</v>
       </c>
       <c r="H26">
-        <v>400.4157161353595</v>
+        <v>398.78203741111088</v>
       </c>
       <c r="I26">
-        <v>393.08572346557929</v>
+        <v>391.73734504538271</v>
       </c>
       <c r="J26">
-        <v>399.22973859297252</v>
+        <v>394.90196274149793</v>
       </c>
       <c r="K26">
-        <v>396.53801247021448</v>
+        <v>394.76570302101197</v>
       </c>
       <c r="L26">
-        <v>386.20309526779067</v>
+        <v>381.96676810225608</v>
       </c>
       <c r="M26">
-        <v>416.79950046830368</v>
+        <v>412.95057523951073</v>
       </c>
       <c r="N26">
-        <v>432.72454035455593</v>
+        <v>428.25659622443908</v>
       </c>
       <c r="O26">
-        <v>429.88762470381403</v>
+        <v>426.03692628289502</v>
       </c>
       <c r="P26">
-        <v>437.79112308458372</v>
+        <v>434.86402308747802</v>
       </c>
       <c r="Q26">
-        <v>444.45830543362428</v>
+        <v>439.15852291428303</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -1996,52 +1967,52 @@
         <v>42</v>
       </c>
       <c r="B27">
-        <v>367.72230918566947</v>
+        <v>367.74880047860188</v>
       </c>
       <c r="C27">
-        <v>367.72230918566947</v>
+        <v>367.2376550225452</v>
       </c>
       <c r="D27">
-        <v>372.77918332116411</v>
+        <v>372.17674814277132</v>
       </c>
       <c r="E27">
-        <v>416.60113037267888</v>
+        <v>414.49271426865528</v>
       </c>
       <c r="F27">
-        <v>404.32896334132448</v>
+        <v>403.42846260038061</v>
       </c>
       <c r="G27">
-        <v>391.36413721044079</v>
+        <v>390.66513719276702</v>
       </c>
       <c r="H27">
-        <v>394.39868575109602</v>
+        <v>393.29396104893777</v>
       </c>
       <c r="I27">
-        <v>395.36812079749768</v>
+        <v>392.43388205340858</v>
       </c>
       <c r="J27">
-        <v>383.99331264641683</v>
+        <v>382.22352058188812</v>
       </c>
       <c r="K27">
-        <v>397.63150453554908</v>
+        <v>397.4821838318714</v>
       </c>
       <c r="L27">
-        <v>410.43256004292272</v>
+        <v>410.82282559175252</v>
       </c>
       <c r="M27">
-        <v>417.11655366404477</v>
+        <v>418.83019570018718</v>
       </c>
       <c r="N27">
-        <v>425.23371327102512</v>
+        <v>426.74605451800431</v>
       </c>
       <c r="O27">
-        <v>424.28979813332683</v>
+        <v>426.6034389066906</v>
       </c>
       <c r="P27">
-        <v>436.88765408213351</v>
+        <v>440.04939875462708</v>
       </c>
       <c r="Q27">
-        <v>444.94153167256428</v>
+        <v>449.58586987163352</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -2049,52 +2020,52 @@
         <v>43</v>
       </c>
       <c r="B28">
-        <v>297.54033411108031</v>
+        <v>297.2390987840202</v>
       </c>
       <c r="C28">
-        <v>293.29147824536187</v>
+        <v>293.35138415593161</v>
       </c>
       <c r="D28">
-        <v>283.51366043659851</v>
+        <v>283.66604400032469</v>
       </c>
       <c r="E28">
-        <v>277.81698444286337</v>
-      </c>
-      <c r="F28">
-        <v>272.24696455793548</v>
+        <v>277.68429930104247</v>
+      </c>
+      <c r="F28" s="2">
+        <v>272.00240780405261</v>
       </c>
       <c r="G28">
-        <v>283.10215658001192</v>
+        <v>281.71361986527558</v>
       </c>
       <c r="H28">
-        <v>292.47558593647199</v>
+        <v>290.53148736867672</v>
       </c>
       <c r="I28">
-        <v>300.65495540756768</v>
+        <v>298.33351004678428</v>
       </c>
       <c r="J28">
-        <v>277.92831154716771</v>
+        <v>276.28246254223183</v>
       </c>
       <c r="K28">
-        <v>266.59001891757367</v>
+        <v>264.56522954662319</v>
       </c>
       <c r="L28">
-        <v>269.31789815000587</v>
+        <v>269.27824574277668</v>
       </c>
       <c r="M28">
-        <v>262.42388240508751</v>
+        <v>262.17802207440729</v>
       </c>
       <c r="N28">
-        <v>272.15742859500909</v>
+        <v>273.13194241658942</v>
       </c>
       <c r="O28">
-        <v>272.61347506220397</v>
+        <v>273.80030252492571</v>
       </c>
       <c r="P28">
-        <v>277.62671312712502</v>
+        <v>278.86211279658079</v>
       </c>
       <c r="Q28">
-        <v>285.91215898811691</v>
+        <v>286.05979289396811</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -2102,52 +2073,52 @@
         <v>44</v>
       </c>
       <c r="B29">
-        <v>286.08794687470709</v>
+        <v>288.92698756469667</v>
       </c>
       <c r="C29">
-        <v>293.35527161004393</v>
+        <v>293.78087795404178</v>
       </c>
       <c r="D29">
-        <v>282.99392193499</v>
+        <v>284.07623899071359</v>
       </c>
       <c r="E29">
-        <v>276.3139730315628</v>
-      </c>
-      <c r="F29">
-        <v>269.91195615198262</v>
+        <v>277.38050757786942</v>
+      </c>
+      <c r="F29" s="2">
+        <v>270.85095308827141</v>
       </c>
       <c r="G29">
-        <v>284.04253119238223</v>
+        <v>285.29526450463419</v>
       </c>
       <c r="H29">
-        <v>281.93781287729217</v>
+        <v>284.09389416554012</v>
       </c>
       <c r="I29">
-        <v>284.64336999287673</v>
+        <v>286.50935023271722</v>
       </c>
       <c r="J29">
-        <v>271.07237397192353</v>
+        <v>271.67856896837509</v>
       </c>
       <c r="K29">
-        <v>259.70716147027912</v>
+        <v>260.28374287772277</v>
       </c>
       <c r="L29">
-        <v>254.69481018406611</v>
+        <v>256.77896811223508</v>
       </c>
       <c r="M29">
-        <v>252.73329713935561</v>
+        <v>253.1466969242656</v>
       </c>
       <c r="N29">
-        <v>249.97873784662039</v>
+        <v>251.17156977576309</v>
       </c>
       <c r="O29">
-        <v>253.78263218803451</v>
+        <v>254.90550832871591</v>
       </c>
       <c r="P29">
-        <v>258.36401216365209</v>
+        <v>260.157180056968</v>
       </c>
       <c r="Q29">
-        <v>265.58457733032128</v>
+        <v>267.74290514570919</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -2155,52 +2126,52 @@
         <v>45</v>
       </c>
       <c r="B30">
-        <v>296.18212312585217</v>
+        <v>296.85788858999359</v>
       </c>
       <c r="C30">
-        <v>290.97890745056969</v>
+        <v>290.89677040945202</v>
       </c>
       <c r="D30">
-        <v>285.73304181500851</v>
+        <v>285.4637185486381</v>
       </c>
       <c r="E30">
-        <v>283.49852456737511</v>
+        <v>282.48979830679809</v>
       </c>
       <c r="F30">
-        <v>277.81100116459339</v>
+        <v>277.82710779198851</v>
       </c>
       <c r="G30">
-        <v>288.72866562835168</v>
+        <v>288.01550846900852</v>
       </c>
       <c r="H30">
-        <v>289.39002390814301</v>
+        <v>291.04144318707762</v>
       </c>
       <c r="I30">
-        <v>289.20710400251198</v>
+        <v>291.14127595309122</v>
       </c>
       <c r="J30">
-        <v>271.32755537037292</v>
-      </c>
-      <c r="K30">
-        <v>257.80356442027443</v>
+        <v>272.88461001677081</v>
+      </c>
+      <c r="K30" s="2">
+        <v>259.27829468895078</v>
       </c>
       <c r="L30">
-        <v>265.55083292074619</v>
+        <v>265.98729764431579</v>
       </c>
       <c r="M30">
-        <v>260.921283330363</v>
+        <v>260.59673584072971</v>
       </c>
       <c r="N30">
-        <v>259.61848996337937</v>
+        <v>259.69990823032111</v>
       </c>
       <c r="O30">
-        <v>260.84311869650259</v>
+        <v>261.31674428536769</v>
       </c>
       <c r="P30">
-        <v>266.7273994953897</v>
+        <v>268.40140580613343</v>
       </c>
       <c r="Q30">
-        <v>277.39281087214363</v>
+        <v>279.45063231403878</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -2208,52 +2179,52 @@
         <v>46</v>
       </c>
       <c r="B31">
-        <v>289.24396940783299</v>
+        <v>289.4677454873227</v>
       </c>
       <c r="C31">
-        <v>290.67266526610263</v>
+        <v>290.44250918273508</v>
       </c>
       <c r="D31">
-        <v>285.53119907107367</v>
+        <v>285.22951093124021</v>
       </c>
       <c r="E31">
-        <v>283.05097943047377</v>
+        <v>283.14418912491368</v>
       </c>
       <c r="F31">
-        <v>277.68391237256958</v>
+        <v>276.49275101432642</v>
       </c>
       <c r="G31">
-        <v>286.36500999827729</v>
+        <v>287.13437248751541</v>
       </c>
       <c r="H31">
-        <v>288.71503993877752</v>
+        <v>290.58785012061162</v>
       </c>
       <c r="I31">
-        <v>291.24720326610873</v>
+        <v>292.50776470970959</v>
       </c>
       <c r="J31">
-        <v>276.91641462248299</v>
-      </c>
-      <c r="K31">
-        <v>261.62973771825079</v>
+        <v>276.27772553239669</v>
+      </c>
+      <c r="K31" s="2">
+        <v>260.74816970436967</v>
       </c>
       <c r="L31">
-        <v>261.3278977607946</v>
+        <v>261.85783923468261</v>
       </c>
       <c r="M31">
-        <v>254.88157063194561</v>
+        <v>257.61206338274059</v>
       </c>
       <c r="N31">
-        <v>250.2989289884847</v>
+        <v>253.6728550262475</v>
       </c>
       <c r="O31">
-        <v>243.7898055781794</v>
+        <v>245.91597479606901</v>
       </c>
       <c r="P31">
-        <v>250.7152101260474</v>
+        <v>251.801802347912</v>
       </c>
       <c r="Q31">
-        <v>244.68790208758071</v>
+        <v>245.42025338348529</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -2261,52 +2232,52 @@
         <v>47</v>
       </c>
       <c r="B32">
-        <v>283.8170513200406</v>
+        <v>284.48701338540559</v>
       </c>
       <c r="C32">
-        <v>293.39450856486172</v>
+        <v>293.49831057800822</v>
       </c>
       <c r="D32">
-        <v>283.37976116280589</v>
+        <v>283.85526419644452</v>
       </c>
       <c r="E32">
-        <v>277.19694103093519</v>
-      </c>
-      <c r="F32">
-        <v>270.76684022918812</v>
+        <v>277.64931980155689</v>
+      </c>
+      <c r="F32" s="2">
+        <v>271.11586170942678</v>
       </c>
       <c r="G32">
-        <v>283.13508169708979</v>
+        <v>283.37992064120789</v>
       </c>
       <c r="H32">
-        <v>283.19138822550809</v>
+        <v>282.50724589406587</v>
       </c>
       <c r="I32">
-        <v>286.10289849462168</v>
+        <v>285.94667793228399</v>
       </c>
       <c r="J32">
-        <v>276.04859171308487</v>
+        <v>276.49308102417842</v>
       </c>
       <c r="K32">
-        <v>265.26421442539362</v>
+        <v>266.11885688786492</v>
       </c>
       <c r="L32">
-        <v>256.729845442591</v>
+        <v>257.05974183445772</v>
       </c>
       <c r="M32">
-        <v>250.76714766681249</v>
+        <v>251.8810375859251</v>
       </c>
       <c r="N32">
-        <v>245.3656662373734</v>
+        <v>246.49981663620139</v>
       </c>
       <c r="O32">
-        <v>250.24913759339</v>
+        <v>250.60546431904601</v>
       </c>
       <c r="P32">
-        <v>246.88783865484149</v>
+        <v>248.29789926964619</v>
       </c>
       <c r="Q32">
-        <v>252.5042657737684</v>
+        <v>253.708472716382</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -2314,52 +2285,52 @@
         <v>48</v>
       </c>
       <c r="B33">
-        <v>286.68706448035442</v>
+        <v>286.23187772999052</v>
       </c>
       <c r="C33">
-        <v>294.00556870454551</v>
+        <v>293.87637697878432</v>
       </c>
       <c r="D33">
-        <v>284.19030007372879</v>
+        <v>284.16496696426032</v>
       </c>
       <c r="E33">
-        <v>277.33560662644248</v>
-      </c>
-      <c r="F33">
-        <v>271.13498844499247</v>
+        <v>277.60131160060939</v>
+      </c>
+      <c r="F33" s="2">
+        <v>270.91792463423292</v>
       </c>
       <c r="G33">
-        <v>281.98520098712078</v>
+        <v>282.98131695451389</v>
       </c>
       <c r="H33">
-        <v>281.08078300932641</v>
+        <v>281.83565246365691</v>
       </c>
       <c r="I33">
-        <v>283.70242838196498</v>
+        <v>284.78235482779911</v>
       </c>
       <c r="J33">
-        <v>273.58521981272992</v>
+        <v>274.68181013142868</v>
       </c>
       <c r="K33">
-        <v>262.54554840435048</v>
+        <v>265.25589993706382</v>
       </c>
       <c r="L33">
-        <v>255.67400573400221</v>
+        <v>255.77732770792511</v>
       </c>
       <c r="M33">
-        <v>248.75141741514531</v>
-      </c>
-      <c r="N33" s="2">
-        <v>243.5370574648131</v>
+        <v>249.3197975635874</v>
+      </c>
+      <c r="N33">
+        <v>244.02448418337161</v>
       </c>
       <c r="O33">
-        <v>247.5871071246483</v>
+        <v>249.2398538965883</v>
       </c>
       <c r="P33">
-        <v>245.8676878629843</v>
+        <v>246.5820591273133</v>
       </c>
       <c r="Q33">
-        <v>252.26426024175959</v>
+        <v>253.20342980564021</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -2367,52 +2338,52 @@
         <v>49</v>
       </c>
       <c r="B34">
-        <v>289.14047585236352</v>
+        <v>285.29636535847749</v>
       </c>
       <c r="C34">
-        <v>293.94608220256129</v>
+        <v>292.92331376180482</v>
       </c>
       <c r="D34">
-        <v>283.97013417241368</v>
+        <v>282.99337858912509</v>
       </c>
       <c r="E34">
-        <v>277.38876658394202</v>
-      </c>
-      <c r="F34">
-        <v>271.0037146497915</v>
+        <v>276.18969004821491</v>
+      </c>
+      <c r="F34" s="2">
+        <v>270.27463190154651</v>
       </c>
       <c r="G34">
-        <v>283.39567009464969</v>
+        <v>283.28319036402672</v>
       </c>
       <c r="H34">
-        <v>284.41976456891592</v>
+        <v>282.14491237028562</v>
       </c>
       <c r="I34">
-        <v>285.68251550860663</v>
+        <v>285.54488188673128</v>
       </c>
       <c r="J34">
-        <v>277.12863277535502</v>
+        <v>275.68954682166537</v>
       </c>
       <c r="K34">
-        <v>265.14834474639707</v>
+        <v>264.66825092906618</v>
       </c>
       <c r="L34">
-        <v>257.18345214375438</v>
+        <v>255.98823911695641</v>
       </c>
       <c r="M34">
-        <v>251.4357102141542</v>
+        <v>249.79019648103201</v>
       </c>
       <c r="N34">
-        <v>246.9560330909317</v>
+        <v>244.4727473090993</v>
       </c>
       <c r="O34">
-        <v>250.9521178575568</v>
+        <v>248.81706367851879</v>
       </c>
       <c r="P34">
-        <v>249.29992984271141</v>
+        <v>247.148099311777</v>
       </c>
       <c r="Q34">
-        <v>255.5348260237561</v>
+        <v>252.36847352664509</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -2420,52 +2391,52 @@
         <v>50</v>
       </c>
       <c r="B35">
-        <v>285.5158579492533</v>
+        <v>287.2116877410279</v>
       </c>
       <c r="C35">
-        <v>294.45244247203522</v>
+        <v>294.31362065251471</v>
       </c>
       <c r="D35">
-        <v>284.49926474978793</v>
+        <v>284.4386205398103</v>
       </c>
       <c r="E35">
-        <v>278.15180308128618</v>
-      </c>
-      <c r="F35">
-        <v>271.52485625518761</v>
+        <v>278.23522239023771</v>
+      </c>
+      <c r="F35" s="2">
+        <v>271.56261709272121</v>
       </c>
       <c r="G35">
-        <v>283.55150787899322</v>
+        <v>284.39490671732381</v>
       </c>
       <c r="H35">
-        <v>283.40334409554839</v>
+        <v>284.98139955198337</v>
       </c>
       <c r="I35">
-        <v>286.87307693865091</v>
+        <v>288.09087400554591</v>
       </c>
       <c r="J35">
-        <v>276.4868577156123</v>
-      </c>
-      <c r="K35">
-        <v>266.83235700218069</v>
+        <v>277.7188911554075</v>
+      </c>
+      <c r="K35" s="3">
+        <v>269.01756108406289</v>
       </c>
       <c r="L35">
-        <v>260.95781596532169</v>
+        <v>260.03384537492838</v>
       </c>
       <c r="M35">
-        <v>252.71453697085579</v>
+        <v>252.9293421163496</v>
       </c>
       <c r="N35">
-        <v>247.19770506455629</v>
+        <v>247.57456965226291</v>
       </c>
       <c r="O35">
-        <v>250.93871384559421</v>
+        <v>252.4991204973287</v>
       </c>
       <c r="P35">
-        <v>249.03595815846199</v>
+        <v>250.23029337585649</v>
       </c>
       <c r="Q35">
-        <v>252.99950299825809</v>
+        <v>255.70754683623019</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -2473,52 +2444,52 @@
         <v>51</v>
       </c>
       <c r="B36">
-        <v>290.55303299582857</v>
+        <v>286.38972736465712</v>
       </c>
       <c r="C36">
-        <v>293.40674954050502</v>
+        <v>293.05820501819773</v>
       </c>
       <c r="D36">
-        <v>283.38500398578742</v>
+        <v>282.94503478820877</v>
       </c>
       <c r="E36">
-        <v>276.40199377519588</v>
+        <v>276.26442504689328</v>
       </c>
       <c r="F36">
-        <v>270.35093911638648</v>
+        <v>269.91790075488183</v>
       </c>
       <c r="G36">
-        <v>283.32560367075831</v>
+        <v>282.34880167429839</v>
       </c>
       <c r="H36">
-        <v>282.87057192173978</v>
+        <v>281.39392238789679</v>
       </c>
       <c r="I36">
-        <v>285.94847359441178</v>
+        <v>284.1176546757963</v>
       </c>
       <c r="J36">
-        <v>275.16345987097969</v>
-      </c>
-      <c r="K36">
-        <v>266.74325488744802</v>
+        <v>273.62966378326792</v>
+      </c>
+      <c r="K36" s="2">
+        <v>264.05733795334203</v>
       </c>
       <c r="L36">
-        <v>259.57950432576507</v>
+        <v>258.13678974861728</v>
       </c>
       <c r="M36">
-        <v>254.61228876526491</v>
+        <v>251.83759241646939</v>
       </c>
       <c r="N36">
-        <v>250.54831522395489</v>
+        <v>248.2065906746196</v>
       </c>
       <c r="O36">
-        <v>254.69812503960091</v>
+        <v>252.94959142383351</v>
       </c>
       <c r="P36">
-        <v>252.79969881128719</v>
+        <v>250.20091679780359</v>
       </c>
       <c r="Q36">
-        <v>258.73702714133049</v>
+        <v>256.26485131954462</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -2526,52 +2497,52 @@
         <v>52</v>
       </c>
       <c r="B37">
-        <v>287.14750125511102</v>
+        <v>287.93296104464372</v>
       </c>
       <c r="C37">
-        <v>294.22974366499568</v>
+        <v>293.95035549869471</v>
       </c>
       <c r="D37">
-        <v>283.90118650285052</v>
+        <v>284.83566965637732</v>
       </c>
       <c r="E37">
-        <v>277.88469602560968</v>
-      </c>
-      <c r="F37">
-        <v>271.205978620569</v>
+        <v>278.79755960330402</v>
+      </c>
+      <c r="F37" s="2">
+        <v>271.84638424954898</v>
       </c>
       <c r="G37">
-        <v>283.67651164573027</v>
+        <v>284.89614749656698</v>
       </c>
       <c r="H37">
-        <v>283.75131548937668</v>
+        <v>283.25288547385941</v>
       </c>
       <c r="I37">
-        <v>287.65819274550267</v>
+        <v>286.66946835893469</v>
       </c>
       <c r="J37">
-        <v>275.52841708487091</v>
+        <v>276.20381338897238</v>
       </c>
       <c r="K37">
-        <v>264.96472528573861</v>
+        <v>268.04455564766522</v>
       </c>
       <c r="L37">
-        <v>258.59262241287252</v>
+        <v>259.61486962101691</v>
       </c>
       <c r="M37">
-        <v>253.4798376911219</v>
+        <v>254.28253636115451</v>
       </c>
       <c r="N37">
-        <v>248.96468107574199</v>
+        <v>249.4096110833641</v>
       </c>
       <c r="O37">
-        <v>252.36645643972591</v>
+        <v>252.46727007387321</v>
       </c>
       <c r="P37">
-        <v>250.10117589042511</v>
+        <v>250.08915082653641</v>
       </c>
       <c r="Q37">
-        <v>257.45007366459288</v>
+        <v>257.66712583659148</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -2579,52 +2550,52 @@
         <v>53</v>
       </c>
       <c r="B38">
-        <v>285.08611730434887</v>
+        <v>285.04670495583031</v>
       </c>
       <c r="C38">
-        <v>293.78341205162059</v>
+        <v>294.44864121510619</v>
       </c>
       <c r="D38">
-        <v>283.36735197320752</v>
+        <v>284.06501495805833</v>
       </c>
       <c r="E38">
-        <v>276.09488438704352</v>
+        <v>277.35006383575819</v>
       </c>
       <c r="F38">
-        <v>269.74556293821382</v>
+        <v>270.7852793864991</v>
       </c>
       <c r="G38">
-        <v>281.21033857738729</v>
+        <v>282.12586215055461</v>
       </c>
       <c r="H38">
-        <v>279.80206949010011</v>
+        <v>281.12238287194589</v>
       </c>
       <c r="I38">
-        <v>282.31414886249422</v>
+        <v>284.69292697842383</v>
       </c>
       <c r="J38">
-        <v>271.56812054285029</v>
-      </c>
-      <c r="K38">
-        <v>263.1647128825465</v>
+        <v>273.89265523671901</v>
+      </c>
+      <c r="K38" s="2">
+        <v>262.08128129010782</v>
       </c>
       <c r="L38">
-        <v>255.29779028123329</v>
+        <v>257.35619621211271</v>
       </c>
       <c r="M38">
-        <v>249.66251040143649</v>
+        <v>251.5529795489702</v>
       </c>
       <c r="N38">
-        <v>244.9940149344016</v>
+        <v>246.68323508284681</v>
       </c>
       <c r="O38">
-        <v>248.004277131393</v>
+        <v>248.78986326593119</v>
       </c>
       <c r="P38">
-        <v>246.0604713649598</v>
+        <v>246.56651767650101</v>
       </c>
       <c r="Q38">
-        <v>253.26696828838001</v>
+        <v>254.01837661321059</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -2632,52 +2603,52 @@
         <v>54</v>
       </c>
       <c r="B39">
-        <v>287.81317209489532</v>
+        <v>286.26462153100158</v>
       </c>
       <c r="C39">
-        <v>293.58005150550241</v>
+        <v>293.51809324516682</v>
       </c>
       <c r="D39">
-        <v>283.92037947699492</v>
+        <v>283.16325224742877</v>
       </c>
       <c r="E39">
-        <v>277.95555083341151</v>
+        <v>276.67493398738901</v>
       </c>
       <c r="F39">
-        <v>271.11523157644558</v>
+        <v>270.28983348449378</v>
       </c>
       <c r="G39">
-        <v>283.45119163611679</v>
+        <v>281.4091859610773</v>
       </c>
       <c r="H39">
-        <v>283.7539630882103</v>
+        <v>281.1722790716293</v>
       </c>
       <c r="I39">
-        <v>285.97078075902851</v>
+        <v>283.9249194558447</v>
       </c>
       <c r="J39">
-        <v>276.30762220541459</v>
-      </c>
-      <c r="K39">
-        <v>265.31572019091618</v>
+        <v>273.19067651747969</v>
+      </c>
+      <c r="K39" s="2">
+        <v>264.08221475465399</v>
       </c>
       <c r="L39">
-        <v>258.53551366320153</v>
+        <v>257.57899459572451</v>
       </c>
       <c r="M39">
-        <v>251.58461185525309</v>
+        <v>251.66576945867979</v>
       </c>
       <c r="N39">
-        <v>246.66720015513101</v>
+        <v>246.14673029080731</v>
       </c>
       <c r="O39">
-        <v>250.30742555201741</v>
+        <v>248.9814526745723</v>
       </c>
       <c r="P39">
-        <v>247.31505349289961</v>
+        <v>246.92039066594069</v>
       </c>
       <c r="Q39">
-        <v>254.26055268930591</v>
+        <v>254.49932991614139</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -2685,52 +2656,52 @@
         <v>55</v>
       </c>
       <c r="B40">
-        <v>284.15975782051612</v>
+        <v>285.24202014968421</v>
       </c>
       <c r="C40">
-        <v>293.55345782062068</v>
+        <v>293.792862665683</v>
       </c>
       <c r="D40">
-        <v>283.12073797451762</v>
+        <v>283.67497558401232</v>
       </c>
       <c r="E40">
-        <v>275.92264223985973</v>
+        <v>276.21535686333362</v>
       </c>
       <c r="F40">
-        <v>269.77593472881438</v>
+        <v>269.77090825255033</v>
       </c>
       <c r="G40">
-        <v>282.07963849776843</v>
+        <v>282.23284530102791</v>
       </c>
       <c r="H40">
-        <v>281.19197989845162</v>
+        <v>281.59010047208221</v>
       </c>
       <c r="I40">
-        <v>283.28299329098559</v>
+        <v>283.82246220454527</v>
       </c>
       <c r="J40">
-        <v>273.67499389764441</v>
-      </c>
-      <c r="K40">
-        <v>264.23866823930928</v>
+        <v>274.69832378134879</v>
+      </c>
+      <c r="K40" s="2">
+        <v>265.17184767936698</v>
       </c>
       <c r="L40">
-        <v>257.78107034627772</v>
+        <v>259.82195954817439</v>
       </c>
       <c r="M40">
-        <v>250.39441243235331</v>
+        <v>251.3600517204265</v>
       </c>
       <c r="N40">
-        <v>245.39229225076201</v>
+        <v>245.9799471717337</v>
       </c>
       <c r="O40">
-        <v>249.22887755757529</v>
+        <v>248.91737075021919</v>
       </c>
       <c r="P40">
-        <v>247.26053966527539</v>
+        <v>245.63091911513021</v>
       </c>
       <c r="Q40">
-        <v>254.7108747088248</v>
+        <v>253.85558299315619</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -2738,52 +2709,52 @@
         <v>56</v>
       </c>
       <c r="B41">
-        <v>291.75182565920687</v>
+        <v>291.48121713349258</v>
       </c>
       <c r="C41">
-        <v>288.57042573085198</v>
+        <v>289.27872622515872</v>
       </c>
       <c r="D41">
-        <v>278.55343341223733</v>
-      </c>
-      <c r="E41">
-        <v>265.46733787015688</v>
+        <v>279.1087556823324</v>
+      </c>
+      <c r="E41" s="2">
+        <v>265.53033575018128</v>
       </c>
       <c r="F41">
-        <v>270.28836213739118</v>
+        <v>270.23317635201062</v>
       </c>
       <c r="G41">
-        <v>283.50449893593873</v>
+        <v>284.98222046767643</v>
       </c>
       <c r="H41">
-        <v>302.2172720139049</v>
+        <v>301.90130142516949</v>
       </c>
       <c r="I41">
-        <v>294.36159069506652</v>
+        <v>294.51989404600732</v>
       </c>
       <c r="J41">
-        <v>291.74433872911999</v>
+        <v>292.55014757242299</v>
       </c>
       <c r="K41">
-        <v>289.94780448020992</v>
+        <v>290.94952049269278</v>
       </c>
       <c r="L41">
-        <v>284.14706587063972</v>
+        <v>285.69127903249932</v>
       </c>
       <c r="M41">
-        <v>291.90385115726639</v>
+        <v>293.48001275202643</v>
       </c>
       <c r="N41">
-        <v>294.46681196795078</v>
+        <v>295.52766078271048</v>
       </c>
       <c r="O41">
-        <v>296.70605593339229</v>
+        <v>298.18098095920681</v>
       </c>
       <c r="P41">
-        <v>297.7995959645113</v>
+        <v>299.15028271512551</v>
       </c>
       <c r="Q41">
-        <v>300.59669630985218</v>
+        <v>302.15638151362378</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -2791,52 +2762,52 @@
         <v>57</v>
       </c>
       <c r="B42">
-        <v>285.72813091370813</v>
+        <v>285.78723450160169</v>
       </c>
       <c r="C42">
-        <v>288.89014752592811</v>
+        <v>288.73028355091401</v>
       </c>
       <c r="D42">
-        <v>277.74946914348823</v>
-      </c>
-      <c r="E42">
-        <v>265.75306282678349</v>
+        <v>279.39697160686973</v>
+      </c>
+      <c r="E42" s="2">
+        <v>267.22406903301771</v>
       </c>
       <c r="F42">
-        <v>272.05247364216132</v>
+        <v>274.19673838762122</v>
       </c>
       <c r="G42">
-        <v>283.50671366617053</v>
+        <v>286.04965523268203</v>
       </c>
       <c r="H42">
-        <v>275.37587237691389</v>
+        <v>278.07846173940868</v>
       </c>
       <c r="I42">
-        <v>267.65224852766221</v>
+        <v>270.23469430111112</v>
       </c>
       <c r="J42">
-        <v>266.30475879102119</v>
+        <v>267.0606365852239</v>
       </c>
       <c r="K42">
-        <v>267.19042511062548</v>
+        <v>267.98227838776432</v>
       </c>
       <c r="L42">
-        <v>259.36568615087822</v>
+        <v>260.11743242839322</v>
       </c>
       <c r="M42">
-        <v>260.43048086683291</v>
+        <v>259.46508437790538</v>
       </c>
       <c r="N42">
-        <v>251.59316562407321</v>
+        <v>250.53071738204159</v>
       </c>
       <c r="O42">
-        <v>245.84482488263501</v>
+        <v>244.26959943111351</v>
       </c>
       <c r="P42">
-        <v>243.80453906742031</v>
+        <v>240.50347815080701</v>
       </c>
       <c r="Q42">
-        <v>247.55988543687809</v>
+        <v>244.87846777862879</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -2844,52 +2815,52 @@
         <v>58</v>
       </c>
       <c r="B43">
-        <v>283.76738105400221</v>
+        <v>283.55789281365389</v>
       </c>
       <c r="C43">
-        <v>287.99842558427332</v>
+        <v>288.65421160357471</v>
       </c>
       <c r="D43">
-        <v>277.9953674176125</v>
-      </c>
-      <c r="E43">
-        <v>266.14566101117668</v>
+        <v>279.97514953765051</v>
+      </c>
+      <c r="E43" s="2">
+        <v>266.89589762166952</v>
       </c>
       <c r="F43">
-        <v>272.75407539112268</v>
+        <v>273.80629019037423</v>
       </c>
       <c r="G43">
-        <v>284.24997888539428</v>
+        <v>285.01022423566849</v>
       </c>
       <c r="H43">
-        <v>273.82135809683501</v>
+        <v>273.96964885097691</v>
       </c>
       <c r="I43">
-        <v>264.62523239998228</v>
+        <v>264.45015280462019</v>
       </c>
       <c r="J43">
-        <v>267.12912117550172</v>
+        <v>267.15443555999428</v>
       </c>
       <c r="K43">
-        <v>263.29551922375862</v>
+        <v>262.61927782724689</v>
       </c>
       <c r="L43">
-        <v>255.41185617061939</v>
+        <v>254.85823423082539</v>
       </c>
       <c r="M43">
-        <v>257.78742171208279</v>
+        <v>256.93216747853683</v>
       </c>
       <c r="N43">
-        <v>247.99101065916301</v>
+        <v>246.0875039338865</v>
       </c>
       <c r="O43">
-        <v>245.85495571386201</v>
+        <v>244.53573962491711</v>
       </c>
       <c r="P43">
-        <v>243.2285156665435</v>
+        <v>241.34454539754611</v>
       </c>
       <c r="Q43">
-        <v>246.28998783109961</v>
+        <v>243.78994954701719</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -2897,52 +2868,52 @@
         <v>59</v>
       </c>
       <c r="B44">
-        <v>293.51508514242249</v>
+        <v>292.00693442135707</v>
       </c>
       <c r="C44">
-        <v>294.06259509603768</v>
+        <v>293.68557819237628</v>
       </c>
       <c r="D44">
-        <v>291.66820993539858</v>
+        <v>291.88371731157571</v>
       </c>
       <c r="E44">
-        <v>277.09736875745079</v>
+        <v>276.67777467270491</v>
       </c>
       <c r="F44">
-        <v>275.4834391662252</v>
+        <v>274.71818483850541</v>
       </c>
       <c r="G44">
-        <v>276.00325955335342</v>
-      </c>
-      <c r="H44">
-        <v>268.337365431411</v>
+        <v>275.14609512599878</v>
+      </c>
+      <c r="H44" s="2">
+        <v>267.67833395952749</v>
       </c>
       <c r="I44">
-        <v>269.67328031173793</v>
+        <v>268.96608551843929</v>
       </c>
       <c r="J44">
-        <v>271.51330571029428</v>
+        <v>269.88274169577988</v>
       </c>
       <c r="K44">
-        <v>275.24184732922288</v>
+        <v>272.40640270827453</v>
       </c>
       <c r="L44">
-        <v>279.48603222961799</v>
+        <v>277.13770555139712</v>
       </c>
       <c r="M44">
-        <v>277.15149530478038</v>
+        <v>274.20700848607748</v>
       </c>
       <c r="N44">
-        <v>278.83902802330181</v>
+        <v>275.88204240647752</v>
       </c>
       <c r="O44">
-        <v>278.96468266025983</v>
+        <v>276.8128143314467</v>
       </c>
       <c r="P44">
-        <v>283.12210683477332</v>
+        <v>281.26564298541962</v>
       </c>
       <c r="Q44">
-        <v>293.3944046456246</v>
+        <v>290.75172571663973</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -2950,52 +2921,52 @@
         <v>60</v>
       </c>
       <c r="B45">
-        <v>294.57546412045423</v>
+        <v>293.91979960306071</v>
       </c>
       <c r="C45">
-        <v>294.13557121999622</v>
+        <v>293.59342419253738</v>
       </c>
       <c r="D45">
-        <v>285.77611605588851</v>
+        <v>284.68858830373961</v>
       </c>
       <c r="E45">
-        <v>285.78580253135169</v>
+        <v>284.20579564162131</v>
       </c>
       <c r="F45">
-        <v>290.60610432309011</v>
+        <v>289.50120375756961</v>
       </c>
       <c r="G45">
-        <v>295.82442692468351</v>
+        <v>295.89118558625518</v>
       </c>
       <c r="H45">
-        <v>303.03909474018161</v>
+        <v>301.82351589942209</v>
       </c>
       <c r="I45">
-        <v>305.27650032860771</v>
+        <v>303.85257725678269</v>
       </c>
       <c r="J45">
-        <v>306.22051108902809</v>
+        <v>304.77896998579638</v>
       </c>
       <c r="K45">
-        <v>309.07578337567031</v>
+        <v>307.54740595001988</v>
       </c>
       <c r="L45">
-        <v>323.09332771374682</v>
+        <v>321.97005917482312</v>
       </c>
       <c r="M45">
-        <v>328.87593322668027</v>
+        <v>328.40324697194433</v>
       </c>
       <c r="N45">
-        <v>331.32817929718271</v>
+        <v>331.11052726105322</v>
       </c>
       <c r="O45">
-        <v>339.39763081922189</v>
+        <v>339.3720503533649</v>
       </c>
       <c r="P45">
-        <v>342.20530894969357</v>
+        <v>344.53896763367737</v>
       </c>
       <c r="Q45">
-        <v>337.85301751530432</v>
+        <v>340.80492748761827</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -3003,52 +2974,52 @@
         <v>61</v>
       </c>
       <c r="B46">
-        <v>305.93816110602103</v>
+        <v>306.36492568251788</v>
       </c>
       <c r="C46">
-        <v>312.45158409711428</v>
+        <v>313.0029897320448</v>
       </c>
       <c r="D46">
-        <v>289.7133719375114</v>
+        <v>290.10866426176392</v>
       </c>
       <c r="E46">
-        <v>289.70513730760803</v>
+        <v>289.55583732755241</v>
       </c>
       <c r="F46">
-        <v>297.32470002546393</v>
+        <v>296.91912866346149</v>
       </c>
       <c r="G46">
-        <v>308.95028903580049</v>
+        <v>308.53892383810108</v>
       </c>
       <c r="H46">
-        <v>305.41128016652391</v>
+        <v>305.59013479196949</v>
       </c>
       <c r="I46">
-        <v>297.84580879404882</v>
+        <v>299.60689953106697</v>
       </c>
       <c r="J46">
-        <v>300.6110238619317</v>
+        <v>302.41522730420547</v>
       </c>
       <c r="K46">
-        <v>318.58345092133709</v>
+        <v>317.33997904569469</v>
       </c>
       <c r="L46">
-        <v>325.89099442163808</v>
+        <v>323.95377002189502</v>
       </c>
       <c r="M46">
-        <v>328.84584006734548</v>
+        <v>327.5735903245187</v>
       </c>
       <c r="N46">
-        <v>337.04813994347188</v>
+        <v>335.80932142174868</v>
       </c>
       <c r="O46">
-        <v>343.8191047035391</v>
+        <v>340.94776251127371</v>
       </c>
       <c r="P46">
-        <v>341.37597037724731</v>
+        <v>338.3315858180369</v>
       </c>
       <c r="Q46">
-        <v>339.96471854014021</v>
+        <v>335.93416631027537</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -3056,57 +3027,57 @@
         <v>62</v>
       </c>
       <c r="B47">
-        <v>296.21132914079169</v>
+        <v>297.97815841813019</v>
       </c>
       <c r="C47">
-        <v>290.29925469315981</v>
+        <v>290.1083231237775</v>
       </c>
       <c r="D47">
-        <v>288.36282481550148</v>
+        <v>288.61612849135059</v>
       </c>
       <c r="E47">
-        <v>289.82602784423182</v>
+        <v>290.25476912428741</v>
       </c>
       <c r="F47">
-        <v>290.49196952583299</v>
+        <v>290.92322658912758</v>
       </c>
       <c r="G47">
-        <v>297.67832949917408</v>
+        <v>296.99728490754421</v>
       </c>
       <c r="H47">
-        <v>296.61678587435961</v>
+        <v>296.02216054283952</v>
       </c>
       <c r="I47">
-        <v>292.92725721183109</v>
+        <v>291.94290484950261</v>
       </c>
       <c r="J47">
-        <v>291.52029182196628</v>
+        <v>291.04993573154741</v>
       </c>
       <c r="K47">
-        <v>305.84326619357859</v>
+        <v>305.90678025980122</v>
       </c>
       <c r="L47">
-        <v>303.20415196039932</v>
+        <v>304.81341256310679</v>
       </c>
       <c r="M47">
-        <v>305.00721548074188</v>
+        <v>307.35129459971682</v>
       </c>
       <c r="N47">
-        <v>308.29169421215528</v>
+        <v>310.19178751881913</v>
       </c>
       <c r="O47">
-        <v>308.40137258645478</v>
+        <v>309.2363003919229</v>
       </c>
       <c r="P47">
-        <v>308.49286961071567</v>
+        <v>310.5886015340285</v>
       </c>
       <c r="Q47">
-        <v>311.6280324434573</v>
+        <v>312.84961538727879</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:Q32 C34:Q47 C33:M33 O33:Q33">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="C2:Q47">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3116,7 +3087,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" bottom="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_RMSEP.xlsx
@@ -1,220 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\trans.alpha.carotenes\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>RMSEP_glo</t>
-  </si>
-  <si>
-    <t>LV1_RMSEP</t>
-  </si>
-  <si>
-    <t>LV2_RMSEP</t>
-  </si>
-  <si>
-    <t>LV3_RMSEP</t>
-  </si>
-  <si>
-    <t>LV4_RMSEP</t>
-  </si>
-  <si>
-    <t>LV5_RMSEP</t>
-  </si>
-  <si>
-    <t>LV6_RMSEP</t>
-  </si>
-  <si>
-    <t>LV7_RMSEP</t>
-  </si>
-  <si>
-    <t>LV8_RMSEP</t>
-  </si>
-  <si>
-    <t>LV9_RMSEP</t>
-  </si>
-  <si>
-    <t>LV10_RMSEP</t>
-  </si>
-  <si>
-    <t>LV11_RMSEP</t>
-  </si>
-  <si>
-    <t>LV12_RMSEP</t>
-  </si>
-  <si>
-    <t>LV13_RMSEP</t>
-  </si>
-  <si>
-    <t>LV14_RMSEP</t>
-  </si>
-  <si>
-    <t>LV15_RMSEP</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -247,51 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -333,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -365,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -400,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -576,2518 +350,2539 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RMSEP_glo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_RMSEP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_RMSEP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_RMSEP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_RMSEP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_RMSEP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_RMSEP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_RMSEP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_RMSEP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_RMSEP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_RMSEP</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_RMSEP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_RMSEP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_RMSEP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_RMSEP</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_RMSEP</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_RMSEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>287.33704720169249</v>
+        <v>289.0641905128132</v>
       </c>
       <c r="C2">
-        <v>323.49213912576198</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D2">
-        <v>295.04093307838559</v>
+        <v>322.8899873598787</v>
       </c>
       <c r="E2">
-        <v>287.70529007381322</v>
-      </c>
-      <c r="F2" s="3">
-        <v>278.03377061857952</v>
+        <v>294.0309892078767</v>
+      </c>
+      <c r="F2">
+        <v>286.875549756326</v>
       </c>
       <c r="G2">
-        <v>273.69458192963492</v>
-      </c>
-      <c r="H2" s="2">
-        <v>262.50860918474382</v>
+        <v>277.7176480160618</v>
+      </c>
+      <c r="H2">
+        <v>271.8831420398108</v>
       </c>
       <c r="I2">
-        <v>261.80208175012763</v>
+        <v>260.4943694209683</v>
       </c>
       <c r="J2">
-        <v>265.7992499779441</v>
+        <v>259.8225991227947</v>
       </c>
       <c r="K2">
-        <v>269.00795139527293</v>
+        <v>264.6742391854642</v>
       </c>
       <c r="L2">
-        <v>272.24428907605522</v>
+        <v>266.4685589993771</v>
       </c>
       <c r="M2">
-        <v>265.45717390083968</v>
+        <v>269.7589696880997</v>
       </c>
       <c r="N2">
-        <v>272.98967703649362</v>
+        <v>262.4609235595419</v>
       </c>
       <c r="O2">
-        <v>270.00632522751562</v>
+        <v>270.4528117030173</v>
       </c>
       <c r="P2">
-        <v>272.82327398254739</v>
+        <v>266.5922784629614</v>
       </c>
       <c r="Q2">
-        <v>268.34106624489777</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
+        <v>268.7569539058704</v>
+      </c>
+      <c r="R2">
+        <v>265.4770602656898</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>303.51840457796311</v>
+        <v>305.4179429420244</v>
       </c>
       <c r="C3">
-        <v>310.75110893808028</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D3">
-        <v>289.49288471354322</v>
+        <v>311.7839948749861</v>
       </c>
       <c r="E3">
-        <v>287.00148349428309</v>
+        <v>290.60419660025</v>
       </c>
       <c r="F3">
-        <v>290.16559185892987</v>
+        <v>287.8591952137853</v>
       </c>
       <c r="G3">
-        <v>298.57095910458031</v>
+        <v>288.1872843611461</v>
       </c>
       <c r="H3">
-        <v>292.02034953161132</v>
+        <v>298.0287257077408</v>
       </c>
       <c r="I3">
-        <v>297.97019361070181</v>
+        <v>291.9214863945319</v>
       </c>
       <c r="J3">
-        <v>301.7162738914987</v>
+        <v>298.719474415608</v>
       </c>
       <c r="K3">
-        <v>301.9477725547568</v>
+        <v>303.1328744296591</v>
       </c>
       <c r="L3">
-        <v>302.76287305081621</v>
+        <v>303.1316565538349</v>
       </c>
       <c r="M3">
-        <v>309.18167051190699</v>
+        <v>303.0819948198653</v>
       </c>
       <c r="N3">
-        <v>314.87215642520931</v>
+        <v>310.5757885638999</v>
       </c>
       <c r="O3">
-        <v>322.87916939798919</v>
+        <v>315.6205910034976</v>
       </c>
       <c r="P3">
-        <v>331.1174112088612</v>
+        <v>323.9089629540077</v>
       </c>
       <c r="Q3">
-        <v>334.38174165678521</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
+        <v>333.3373741592962</v>
+      </c>
+      <c r="R3">
+        <v>337.2117537102951</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>329.44532436495979</v>
+        <v>324.8827066204246</v>
       </c>
       <c r="C4">
-        <v>320.13040897203012</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D4">
-        <v>299.83486512456841</v>
+        <v>319.6150635304709</v>
       </c>
       <c r="E4">
-        <v>297.01639211765348</v>
+        <v>298.7835404610548</v>
       </c>
       <c r="F4">
-        <v>301.27445015451411</v>
+        <v>296.2294102217186</v>
       </c>
       <c r="G4">
-        <v>297.00809399430489</v>
+        <v>300.6997221683415</v>
       </c>
       <c r="H4">
-        <v>299.30024209962869</v>
+        <v>295.1692889503208</v>
       </c>
       <c r="I4">
-        <v>292.00406474996868</v>
+        <v>296.4514663926348</v>
       </c>
       <c r="J4">
-        <v>292.07024998400698</v>
+        <v>289.6503504194063</v>
       </c>
       <c r="K4">
-        <v>290.53213050608019</v>
+        <v>289.093927669992</v>
       </c>
       <c r="L4">
-        <v>301.90150686793078</v>
+        <v>287.7058913215228</v>
       </c>
       <c r="M4">
-        <v>301.98018125749269</v>
+        <v>299.0489748915585</v>
       </c>
       <c r="N4">
-        <v>299.95045466729289</v>
+        <v>300.129428393862</v>
       </c>
       <c r="O4">
-        <v>295.52702510131769</v>
+        <v>297.3751828483243</v>
       </c>
       <c r="P4">
-        <v>298.26731441115339</v>
+        <v>293.2315521810881</v>
       </c>
       <c r="Q4">
-        <v>305.90704744078511</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
+        <v>294.3834332182029</v>
+      </c>
+      <c r="R4">
+        <v>301.0662985088022</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>295.49909337505738</v>
+        <v>296.4729940647215</v>
       </c>
       <c r="C5">
-        <v>292.95100426237991</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D5">
-        <v>292.2259951221954</v>
+        <v>293.307097228544</v>
       </c>
       <c r="E5">
-        <v>291.9022951352855</v>
+        <v>293.2520931380346</v>
       </c>
       <c r="F5">
-        <v>299.50345863504009</v>
+        <v>293.0653459037091</v>
       </c>
       <c r="G5">
-        <v>300.45067837178931</v>
+        <v>301.237181591077</v>
       </c>
       <c r="H5">
-        <v>306.32613648356249</v>
+        <v>301.2171287391238</v>
       </c>
       <c r="I5">
-        <v>305.90242321321762</v>
+        <v>304.5842485695308</v>
       </c>
       <c r="J5">
-        <v>296.52888866687522</v>
+        <v>304.4227255298611</v>
       </c>
       <c r="K5">
-        <v>292.03207477908501</v>
+        <v>295.4300036766144</v>
       </c>
       <c r="L5">
-        <v>296.2385786228935</v>
+        <v>290.9938081873511</v>
       </c>
       <c r="M5">
-        <v>297.39049970221868</v>
+        <v>295.9860648094558</v>
       </c>
       <c r="N5">
-        <v>301.35806705288991</v>
+        <v>296.1332804366822</v>
       </c>
       <c r="O5">
-        <v>309.30653465299162</v>
+        <v>299.3320187429813</v>
       </c>
       <c r="P5">
-        <v>307.62167034418309</v>
+        <v>306.0445001828303</v>
       </c>
       <c r="Q5">
-        <v>312.26577305838839</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
+        <v>304.8367522150357</v>
+      </c>
+      <c r="R5">
+        <v>309.0689636060444</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>297.32790475229268</v>
+        <v>300.5055394179832</v>
       </c>
       <c r="C6">
-        <v>292.08123282486758</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D6">
-        <v>289.64562844346591</v>
+        <v>292.5687859934341</v>
       </c>
       <c r="E6">
-        <v>289.16728309470801</v>
+        <v>290.4895109626803</v>
       </c>
       <c r="F6">
-        <v>309.3246784246453</v>
+        <v>289.9348854071249</v>
       </c>
       <c r="G6">
-        <v>297.82011193629899</v>
+        <v>309.9803771326195</v>
       </c>
       <c r="H6">
-        <v>306.29851048921341</v>
+        <v>297.8952113444647</v>
       </c>
       <c r="I6">
-        <v>298.29543159167531</v>
+        <v>303.6605477928479</v>
       </c>
       <c r="J6">
-        <v>287.77905025589502</v>
+        <v>297.2589062775389</v>
       </c>
       <c r="K6">
-        <v>291.40494986579728</v>
+        <v>286.726575998132</v>
       </c>
       <c r="L6">
-        <v>294.73771585789189</v>
+        <v>289.5730733289546</v>
       </c>
       <c r="M6">
-        <v>300.32974959215397</v>
+        <v>293.3276614688554</v>
       </c>
       <c r="N6">
-        <v>306.57776566388458</v>
+        <v>300.3924527144438</v>
       </c>
       <c r="O6">
-        <v>309.10366420858333</v>
+        <v>305.8610367307995</v>
       </c>
       <c r="P6">
-        <v>308.89900992580931</v>
+        <v>307.9140493888954</v>
       </c>
       <c r="Q6">
-        <v>301.73683086458152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
+        <v>308.3243910590696</v>
+      </c>
+      <c r="R6">
+        <v>301.0944362174116</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>284.36132164142538</v>
+        <v>285.6610316670029</v>
       </c>
       <c r="C7">
-        <v>319.95382054700258</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D7">
-        <v>295.51678589055513</v>
+        <v>320.1026345143292</v>
       </c>
       <c r="E7">
-        <v>282.26834370240152</v>
+        <v>296.0848667123014</v>
       </c>
       <c r="F7">
-        <v>273.87708484767251</v>
+        <v>282.8642975470815</v>
       </c>
       <c r="G7">
-        <v>270.70911064731638</v>
-      </c>
-      <c r="H7" s="2">
-        <v>263.60094432348222</v>
+        <v>274.7255961268612</v>
+      </c>
+      <c r="H7">
+        <v>272.6720632867429</v>
       </c>
       <c r="I7">
-        <v>270.74025065638989</v>
+        <v>263.6917731364787</v>
       </c>
       <c r="J7">
-        <v>264.42581098999312</v>
+        <v>272.2382348201402</v>
       </c>
       <c r="K7">
-        <v>262.77655621138132</v>
+        <v>265.8868903637781</v>
       </c>
       <c r="L7">
-        <v>263.32617431363298</v>
+        <v>264.2677692680401</v>
       </c>
       <c r="M7">
-        <v>266.06058517356098</v>
+        <v>263.4391720217516</v>
       </c>
       <c r="N7">
-        <v>271.13981262181818</v>
+        <v>265.9166248366845</v>
       </c>
       <c r="O7">
-        <v>266.03952187321852</v>
+        <v>271.131424939837</v>
       </c>
       <c r="P7">
-        <v>260.99005427139667</v>
+        <v>265.710765704927</v>
       </c>
       <c r="Q7">
-        <v>263.83778104992211</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
+        <v>260.4157509677433</v>
+      </c>
+      <c r="R7">
+        <v>262.7182196695229</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>317.28464655638339</v>
+        <v>317.9080621398788</v>
       </c>
       <c r="C8">
-        <v>310.31952178960569</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D8">
-        <v>300.11079595523063</v>
+        <v>309.8891916190652</v>
       </c>
       <c r="E8">
-        <v>299.80442536948959</v>
+        <v>300.030619854117</v>
       </c>
       <c r="F8">
-        <v>295.95414785720811</v>
+        <v>299.0190501266043</v>
       </c>
       <c r="G8">
-        <v>283.44690690119131</v>
+        <v>294.8129246732493</v>
       </c>
       <c r="H8">
-        <v>290.49864891675378</v>
+        <v>283.3016700075076</v>
       </c>
       <c r="I8">
-        <v>281.83784902906109</v>
+        <v>290.0463503242095</v>
       </c>
       <c r="J8">
-        <v>278.83118377871978</v>
+        <v>281.8981593084307</v>
       </c>
       <c r="K8">
-        <v>284.01725371999089</v>
+        <v>277.7876133952398</v>
       </c>
       <c r="L8">
-        <v>286.17144986649259</v>
+        <v>283.2390162922122</v>
       </c>
       <c r="M8">
-        <v>288.0814905394576</v>
+        <v>285.9401265695256</v>
       </c>
       <c r="N8">
-        <v>285.67090457571891</v>
+        <v>287.4205929131768</v>
       </c>
       <c r="O8">
-        <v>284.0234166301135</v>
+        <v>285.6913285677203</v>
       </c>
       <c r="P8">
-        <v>284.46389570541862</v>
+        <v>282.2910813244855</v>
       </c>
       <c r="Q8">
-        <v>289.92629839113249</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
+        <v>282.6303065004003</v>
+      </c>
+      <c r="R8">
+        <v>288.2158693493863</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>317.82413238213309</v>
+        <v>314.1102481325286</v>
       </c>
       <c r="C9">
-        <v>310.80881203851573</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D9">
-        <v>300.99100489508572</v>
+        <v>310.5701937301022</v>
       </c>
       <c r="E9">
-        <v>300.62974722494732</v>
+        <v>300.1495100431916</v>
       </c>
       <c r="F9">
-        <v>296.63694537655812</v>
+        <v>298.9986223574002</v>
       </c>
       <c r="G9">
-        <v>285.58021096014522</v>
+        <v>295.0921917178144</v>
       </c>
       <c r="H9">
-        <v>292.08043798303532</v>
+        <v>283.2906442775605</v>
       </c>
       <c r="I9">
-        <v>283.62407928305697</v>
+        <v>289.455817199282</v>
       </c>
       <c r="J9">
-        <v>279.60751572308681</v>
+        <v>280.6145418829955</v>
       </c>
       <c r="K9">
-        <v>283.53650680478478</v>
+        <v>277.5605302610907</v>
       </c>
       <c r="L9">
-        <v>287.75151835009649</v>
+        <v>281.0992137661712</v>
       </c>
       <c r="M9">
-        <v>290.11190838671678</v>
+        <v>285.0351780461775</v>
       </c>
       <c r="N9">
-        <v>289.73894712231572</v>
+        <v>288.426877652159</v>
       </c>
       <c r="O9">
-        <v>285.66110265020501</v>
+        <v>286.8775458057951</v>
       </c>
       <c r="P9">
-        <v>278.63380132899158</v>
+        <v>282.1733060907703</v>
       </c>
       <c r="Q9">
-        <v>286.68175988601018</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
+        <v>275.0116373123158</v>
+      </c>
+      <c r="R9">
+        <v>282.1982063712884</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>318.66092073540898</v>
+        <v>315.5588250462027</v>
       </c>
       <c r="C10">
-        <v>310.64397205785212</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D10">
-        <v>300.82708744914157</v>
+        <v>310.3371342938497</v>
       </c>
       <c r="E10">
-        <v>300.11553282308921</v>
+        <v>300.0684845816197</v>
       </c>
       <c r="F10">
-        <v>296.0279599860566</v>
+        <v>298.3977223173786</v>
       </c>
       <c r="G10">
-        <v>284.33044959398171</v>
+        <v>294.2857655498348</v>
       </c>
       <c r="H10">
-        <v>291.23920784650272</v>
+        <v>284.3973888776163</v>
       </c>
       <c r="I10">
-        <v>282.33149698661282</v>
+        <v>289.1244615903018</v>
       </c>
       <c r="J10">
-        <v>278.44605032377171</v>
+        <v>281.4382345851595</v>
       </c>
       <c r="K10">
-        <v>282.57066235286658</v>
+        <v>278.0354889413578</v>
       </c>
       <c r="L10">
-        <v>287.33894934694149</v>
+        <v>282.1229437229614</v>
       </c>
       <c r="M10">
-        <v>288.96360706764409</v>
+        <v>285.455412509237</v>
       </c>
       <c r="N10">
-        <v>287.86690635678701</v>
+        <v>287.9077885787041</v>
       </c>
       <c r="O10">
-        <v>282.98790369749793</v>
+        <v>286.3585870605724</v>
       </c>
       <c r="P10">
-        <v>275.43587829761361</v>
+        <v>281.0973017501819</v>
       </c>
       <c r="Q10">
-        <v>282.15817522796141</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
+        <v>274.0395954978021</v>
+      </c>
+      <c r="R10">
+        <v>282.3325245424711</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>317.9921477781445</v>
+        <v>322.1463817211637</v>
       </c>
       <c r="C11">
-        <v>311.02609905205691</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D11">
-        <v>300.51715691768641</v>
+        <v>310.8766518359749</v>
       </c>
       <c r="E11">
-        <v>298.80508695484639</v>
+        <v>300.8172262941727</v>
       </c>
       <c r="F11">
-        <v>294.6082693096738</v>
+        <v>300.7268069508208</v>
       </c>
       <c r="G11">
-        <v>285.4315610830779</v>
+        <v>297.4412387181222</v>
       </c>
       <c r="H11">
-        <v>290.67801997450732</v>
+        <v>287.9053117784373</v>
       </c>
       <c r="I11">
-        <v>282.85662064105622</v>
+        <v>294.1222958172152</v>
       </c>
       <c r="J11">
-        <v>280.09579265325158</v>
+        <v>286.483336774911</v>
       </c>
       <c r="K11">
-        <v>283.50669530677368</v>
+        <v>282.1812753573951</v>
       </c>
       <c r="L11">
-        <v>288.6311648861664</v>
+        <v>285.4488511939612</v>
       </c>
       <c r="M11">
-        <v>291.21181624508381</v>
+        <v>290.5368398883523</v>
       </c>
       <c r="N11">
-        <v>290.00611945739399</v>
+        <v>292.8962063477567</v>
       </c>
       <c r="O11">
-        <v>287.62013054647088</v>
+        <v>290.6421440368785</v>
       </c>
       <c r="P11">
-        <v>284.26019845744861</v>
+        <v>287.6985914375634</v>
       </c>
       <c r="Q11">
-        <v>282.54439979336701</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
+        <v>283.797366557145</v>
+      </c>
+      <c r="R11">
+        <v>282.9825301795112</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>298.47359362435338</v>
+        <v>298.349596446338</v>
       </c>
       <c r="C12">
-        <v>291.40322332073129</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D12">
-        <v>290.89816277183093</v>
+        <v>290.8673028984627</v>
       </c>
       <c r="E12">
-        <v>291.58543190952111</v>
+        <v>289.7914601841709</v>
       </c>
       <c r="F12">
-        <v>301.67169445983308</v>
+        <v>290.1559349708292</v>
       </c>
       <c r="G12">
-        <v>298.80076592072078</v>
+        <v>299.3531570399497</v>
       </c>
       <c r="H12">
-        <v>296.52122230984293</v>
+        <v>296.6851409374793</v>
       </c>
       <c r="I12">
-        <v>292.03502829563843</v>
+        <v>294.4239227717806</v>
       </c>
       <c r="J12">
-        <v>279.93662986380059</v>
+        <v>289.9144327853024</v>
       </c>
       <c r="K12">
-        <v>278.30316404997421</v>
+        <v>276.8458293284594</v>
       </c>
       <c r="L12">
-        <v>276.99064565650121</v>
+        <v>275.8218014357829</v>
       </c>
       <c r="M12">
-        <v>284.84605850512958</v>
+        <v>274.362297270587</v>
       </c>
       <c r="N12">
-        <v>285.49143060523983</v>
+        <v>282.7572599005194</v>
       </c>
       <c r="O12">
-        <v>292.89935656213498</v>
+        <v>283.3017913218431</v>
       </c>
       <c r="P12">
-        <v>294.09953080247948</v>
+        <v>290.4283874218628</v>
       </c>
       <c r="Q12">
-        <v>295.6657766222325</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
+        <v>292.4806216578673</v>
+      </c>
+      <c r="R12">
+        <v>294.6955172906088</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>293.75146902522027</v>
+        <v>295.1439120668398</v>
       </c>
       <c r="C13">
-        <v>290.48251922075201</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D13">
-        <v>285.81531810799743</v>
+        <v>290.517023577334</v>
       </c>
       <c r="E13">
-        <v>283.99090754213353</v>
+        <v>285.655948645321</v>
       </c>
       <c r="F13">
-        <v>286.16790534488399</v>
+        <v>284.2598965481015</v>
       </c>
       <c r="G13">
-        <v>297.61932910291608</v>
+        <v>287.017023691956</v>
       </c>
       <c r="H13">
-        <v>301.01205214165049</v>
+        <v>298.3735237488781</v>
       </c>
       <c r="I13">
-        <v>298.86054685276588</v>
+        <v>301.2998965929897</v>
       </c>
       <c r="J13">
-        <v>292.65790405049648</v>
+        <v>299.8156383432999</v>
       </c>
       <c r="K13">
-        <v>292.28868947763181</v>
+        <v>294.4824532985972</v>
       </c>
       <c r="L13">
-        <v>291.93728388509658</v>
+        <v>293.5858710291851</v>
       </c>
       <c r="M13">
-        <v>290.69770960442008</v>
+        <v>293.4281870571978</v>
       </c>
       <c r="N13">
-        <v>293.30873768835181</v>
+        <v>292.2871400726589</v>
       </c>
       <c r="O13">
-        <v>296.34323825061227</v>
+        <v>295.0407092331673</v>
       </c>
       <c r="P13">
-        <v>299.12644732461598</v>
+        <v>298.5235202817153</v>
       </c>
       <c r="Q13">
-        <v>303.50471596735929</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
+        <v>301.635560439629</v>
+      </c>
+      <c r="R13">
+        <v>306.9408224331985</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>285.19353525365858</v>
+        <v>287.1144218931292</v>
       </c>
       <c r="C14">
-        <v>320.24962396617838</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D14">
-        <v>295.84516436175687</v>
-      </c>
-      <c r="E14" s="2">
-        <v>282.61777551293972</v>
+        <v>319.9426412707742</v>
+      </c>
+      <c r="E14">
+        <v>295.7644925430967</v>
       </c>
       <c r="F14">
-        <v>274.72159347598688</v>
+        <v>283.0717057219177</v>
       </c>
       <c r="G14">
-        <v>271.36801955225229</v>
+        <v>274.2495382756223</v>
       </c>
       <c r="H14">
-        <v>264.3863524906767</v>
+        <v>270.9703620189299</v>
       </c>
       <c r="I14">
-        <v>269.3679168303654</v>
+        <v>265.2469497842856</v>
       </c>
       <c r="J14">
-        <v>264.85372261298858</v>
+        <v>269.8076348884967</v>
       </c>
       <c r="K14">
-        <v>264.58555840344599</v>
+        <v>265.5826819697384</v>
       </c>
       <c r="L14">
-        <v>263.98809296129178</v>
+        <v>264.8804958896784</v>
       </c>
       <c r="M14">
-        <v>269.76304440859138</v>
+        <v>265.6201968606186</v>
       </c>
       <c r="N14">
-        <v>277.86465972078281</v>
+        <v>270.7180418253952</v>
       </c>
       <c r="O14">
-        <v>272.54582868652841</v>
+        <v>278.7769966668459</v>
       </c>
       <c r="P14">
-        <v>264.09932826384778</v>
+        <v>273.4671718948559</v>
       </c>
       <c r="Q14">
-        <v>256.82599951005437</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
+        <v>266.375580897234</v>
+      </c>
+      <c r="R14">
+        <v>260.2082762333341</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>289.42694827808748</v>
+        <v>284.436385852901</v>
       </c>
       <c r="C15">
-        <v>321.33837859449278</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D15">
-        <v>296.90673189484443</v>
-      </c>
-      <c r="E15" s="2">
-        <v>284.59345836634168</v>
+        <v>320.0343146674664</v>
+      </c>
+      <c r="E15">
+        <v>295.18033760131</v>
       </c>
       <c r="F15">
-        <v>275.99955057675419</v>
+        <v>280.9805191421705</v>
       </c>
       <c r="G15">
-        <v>273.13987050971542</v>
+        <v>273.2868633248427</v>
       </c>
       <c r="H15">
-        <v>266.64933676631142</v>
+        <v>269.9556295635504</v>
       </c>
       <c r="I15">
-        <v>273.31509672492501</v>
+        <v>262.6776428523301</v>
       </c>
       <c r="J15">
-        <v>267.41060057504347</v>
+        <v>268.7904600707688</v>
       </c>
       <c r="K15">
-        <v>266.61837165706783</v>
+        <v>264.4708656234299</v>
       </c>
       <c r="L15">
-        <v>267.05655992910869</v>
+        <v>263.8354676806628</v>
       </c>
       <c r="M15">
-        <v>272.37274434124703</v>
+        <v>263.928270623984</v>
       </c>
       <c r="N15">
-        <v>281.47077272855847</v>
+        <v>269.129117194409</v>
       </c>
       <c r="O15">
-        <v>275.34331711131142</v>
+        <v>277.2905829905889</v>
       </c>
       <c r="P15">
-        <v>269.33180288918732</v>
+        <v>270.6004065844554</v>
       </c>
       <c r="Q15">
-        <v>261.95378939897449</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
+        <v>263.0128499840609</v>
+      </c>
+      <c r="R15">
+        <v>257.4862788894213</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>284.87212935285697</v>
+        <v>288.0780408961626</v>
       </c>
       <c r="C16">
-        <v>320.6700788479651</v>
-      </c>
-      <c r="D16" s="3">
-        <v>296.71093417139599</v>
-      </c>
-      <c r="E16" s="2">
-        <v>283.25058498058468</v>
+        <v>373.1884614245382</v>
+      </c>
+      <c r="D16">
+        <v>320.3492299312013</v>
+      </c>
+      <c r="E16">
+        <v>296.620490664929</v>
       </c>
       <c r="F16">
-        <v>274.62792557388798</v>
+        <v>284.2647919427051</v>
       </c>
       <c r="G16">
-        <v>271.58345096092881</v>
+        <v>275.7805370758739</v>
       </c>
       <c r="H16">
-        <v>264.99045675105992</v>
+        <v>274.152877676678</v>
       </c>
       <c r="I16">
-        <v>270.42501009500688</v>
+        <v>266.338636073278</v>
       </c>
       <c r="J16">
-        <v>265.81937055818361</v>
+        <v>272.0935908205436</v>
       </c>
       <c r="K16">
-        <v>265.69687119935782</v>
+        <v>266.7582753152108</v>
       </c>
       <c r="L16">
-        <v>265.82085039634569</v>
+        <v>265.8197964311639</v>
       </c>
       <c r="M16">
-        <v>270.10486316774802</v>
+        <v>265.7768523451695</v>
       </c>
       <c r="N16">
-        <v>279.26676239886348</v>
+        <v>268.834293502037</v>
       </c>
       <c r="O16">
-        <v>273.69066950908802</v>
+        <v>274.8694099693235</v>
       </c>
       <c r="P16">
-        <v>266.04731309215123</v>
+        <v>268.8299874345047</v>
       </c>
       <c r="Q16">
-        <v>260.38064732205652</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
+        <v>262.3875273833536</v>
+      </c>
+      <c r="R16">
+        <v>255.6127766862822</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>287.91687103370708</v>
-      </c>
-      <c r="C17" s="3">
-        <v>320.29260827717007</v>
+        <v>285.4910335393071</v>
+      </c>
+      <c r="C17">
+        <v>373.1884614245382</v>
       </c>
       <c r="D17">
-        <v>296.19612648439721</v>
-      </c>
-      <c r="E17" s="2">
-        <v>283.25468724465537</v>
+        <v>320.2382370540833</v>
+      </c>
+      <c r="E17">
+        <v>296.4420670461159</v>
       </c>
       <c r="F17">
-        <v>274.91498017256959</v>
+        <v>283.0165235315134</v>
       </c>
       <c r="G17">
-        <v>271.99151854243502</v>
+        <v>274.716405574625</v>
       </c>
       <c r="H17">
-        <v>265.99725443962518</v>
+        <v>271.5377864187599</v>
       </c>
       <c r="I17">
-        <v>271.53819739374461</v>
+        <v>265.0530889024047</v>
       </c>
       <c r="J17">
-        <v>266.74436345854411</v>
+        <v>270.8882872924297</v>
       </c>
       <c r="K17">
-        <v>266.53970857894763</v>
+        <v>265.3156148647426</v>
       </c>
       <c r="L17">
-        <v>266.62500226213371</v>
+        <v>264.5734366902591</v>
       </c>
       <c r="M17">
-        <v>272.3952115208142</v>
+        <v>264.2184578505548</v>
       </c>
       <c r="N17">
-        <v>279.75533604520132</v>
+        <v>269.2861108801105</v>
       </c>
       <c r="O17">
-        <v>274.37278419489871</v>
+        <v>276.0462388136221</v>
       </c>
       <c r="P17">
-        <v>267.08052359564812</v>
+        <v>270.253003864818</v>
       </c>
       <c r="Q17">
-        <v>260.96318365491408</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>33</v>
+        <v>262.712687840908</v>
+      </c>
+      <c r="R17">
+        <v>257.5004003644266</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>300.66930679831893</v>
+        <v>297.3118499053472</v>
       </c>
       <c r="C18">
-        <v>290.24118453522289</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D18">
-        <v>290.01624890761309</v>
-      </c>
-      <c r="E18" s="3">
-        <v>291.01656607909479</v>
+        <v>290.3252749390412</v>
+      </c>
+      <c r="E18">
+        <v>289.2822390908096</v>
       </c>
       <c r="F18">
-        <v>299.3777909962152</v>
+        <v>289.9491468220165</v>
       </c>
       <c r="G18">
-        <v>292.7161720839602</v>
+        <v>298.0439331154655</v>
       </c>
       <c r="H18">
-        <v>298.93070149029779</v>
+        <v>292.7034210880868</v>
       </c>
       <c r="I18">
-        <v>287.00305756119332</v>
-      </c>
-      <c r="J18" s="2">
-        <v>275.21923897867009</v>
+        <v>298.4075493407672</v>
+      </c>
+      <c r="J18">
+        <v>285.9955848877032</v>
       </c>
       <c r="K18">
-        <v>267.83786286389858</v>
+        <v>273.565675149137</v>
       </c>
       <c r="L18">
-        <v>264.03433953389401</v>
+        <v>265.6968898065482</v>
       </c>
       <c r="M18">
-        <v>265.92613220971492</v>
+        <v>262.3523717664173</v>
       </c>
       <c r="N18">
-        <v>266.05957389835493</v>
+        <v>262.8872532876936</v>
       </c>
       <c r="O18">
-        <v>271.54832944794038</v>
+        <v>263.5631591179358</v>
       </c>
       <c r="P18">
-        <v>273.38270605797089</v>
+        <v>268.9557171848359</v>
       </c>
       <c r="Q18">
-        <v>274.32569363865173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>34</v>
+        <v>270.9957149791297</v>
+      </c>
+      <c r="R18">
+        <v>272.7750754365816</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>299.51655894955991</v>
+        <v>299.1575516476771</v>
       </c>
       <c r="C19">
-        <v>290.32772587257932</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D19">
-        <v>287.84328747493453</v>
+        <v>290.2930782764905</v>
       </c>
       <c r="E19">
-        <v>287.16750311390467</v>
+        <v>287.9529291682654</v>
       </c>
       <c r="F19">
-        <v>309.26517973957249</v>
+        <v>287.3954495736474</v>
       </c>
       <c r="G19">
-        <v>298.21285864727008</v>
+        <v>308.3197269892887</v>
       </c>
       <c r="H19">
-        <v>292.97628942917669</v>
-      </c>
-      <c r="I19" s="2">
-        <v>272.99361685745532</v>
+        <v>298.0414682105459</v>
+      </c>
+      <c r="I19">
+        <v>291.8247017689322</v>
       </c>
       <c r="J19">
-        <v>271.53434501098718</v>
+        <v>271.7187755434451</v>
       </c>
       <c r="K19">
-        <v>261.23392615448108</v>
+        <v>271.5239931201944</v>
       </c>
       <c r="L19">
-        <v>259.68097803212862</v>
+        <v>261.6991683555284</v>
       </c>
       <c r="M19">
-        <v>264.95566394986002</v>
+        <v>260.1050806138238</v>
       </c>
       <c r="N19">
-        <v>266.56475567842352</v>
+        <v>265.8092411594853</v>
       </c>
       <c r="O19">
-        <v>265.01524019599412</v>
+        <v>268.2112788361048</v>
       </c>
       <c r="P19">
-        <v>266.03271880117882</v>
+        <v>266.9487255511031</v>
       </c>
       <c r="Q19">
-        <v>262.11198216217258</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
+        <v>266.6376592541534</v>
+      </c>
+      <c r="R19">
+        <v>264.0734630501755</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>300.52715482362328</v>
+        <v>295.1252328678898</v>
       </c>
       <c r="C20">
-        <v>291.04951406515278</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D20">
-        <v>288.8771819603171</v>
+        <v>290.8606105888578</v>
       </c>
       <c r="E20">
-        <v>288.69694004967869</v>
+        <v>288.4191751018911</v>
       </c>
       <c r="F20">
-        <v>293.8315717341477</v>
+        <v>287.4826924365295</v>
       </c>
       <c r="G20">
-        <v>298.72882980061519</v>
+        <v>292.1350250794731</v>
       </c>
       <c r="H20">
-        <v>293.69212839002472</v>
-      </c>
-      <c r="I20" s="2">
-        <v>277.28358630799659</v>
-      </c>
-      <c r="J20" s="3">
-        <v>264.47316546506818</v>
+        <v>296.2470079958955</v>
+      </c>
+      <c r="I20">
+        <v>290.4766732398301</v>
+      </c>
+      <c r="J20">
+        <v>276.1358477871262</v>
       </c>
       <c r="K20">
-        <v>257.46515351385779</v>
+        <v>262.190131037746</v>
       </c>
       <c r="L20">
-        <v>262.97182738374062</v>
+        <v>256.1450410552455</v>
       </c>
       <c r="M20">
-        <v>267.44036187806648</v>
+        <v>261.7721227291181</v>
       </c>
       <c r="N20">
-        <v>270.91665730677607</v>
+        <v>263.8667225618685</v>
       </c>
       <c r="O20">
-        <v>271.38825549697822</v>
+        <v>267.526983272945</v>
       </c>
       <c r="P20">
-        <v>264.08633398508641</v>
+        <v>268.0415051501648</v>
       </c>
       <c r="Q20">
-        <v>262.47079115285351</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>36</v>
+        <v>261.8845300201468</v>
+      </c>
+      <c r="R20">
+        <v>259.4677272707606</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>301.86514057562181</v>
+        <v>302.4511660140443</v>
       </c>
       <c r="C21">
-        <v>310.79775624046732</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D21">
-        <v>290.15174418011418</v>
+        <v>311.8787312306509</v>
       </c>
       <c r="E21">
-        <v>286.16109427219169</v>
+        <v>291.0570179588578</v>
       </c>
       <c r="F21">
-        <v>283.49093644535247</v>
+        <v>287.2625286554171</v>
       </c>
       <c r="G21">
-        <v>290.41068721158871</v>
+        <v>284.912578486395</v>
       </c>
       <c r="H21">
-        <v>285.48929277654179</v>
+        <v>291.6716692769952</v>
       </c>
       <c r="I21">
-        <v>294.30949975530842</v>
+        <v>287.1433247488844</v>
       </c>
       <c r="J21">
-        <v>292.89050304632673</v>
+        <v>294.2293364504837</v>
       </c>
       <c r="K21">
-        <v>292.09838043710801</v>
+        <v>292.6780155934629</v>
       </c>
       <c r="L21">
-        <v>298.19742929427531</v>
+        <v>292.3816816521162</v>
       </c>
       <c r="M21">
-        <v>307.49687153681901</v>
+        <v>296.9885200160338</v>
       </c>
       <c r="N21">
-        <v>312.11493689727729</v>
+        <v>306.0564798887921</v>
       </c>
       <c r="O21">
-        <v>323.97342795284789</v>
+        <v>308.8865495228752</v>
       </c>
       <c r="P21">
-        <v>331.70229027341782</v>
+        <v>321.1733830882592</v>
       </c>
       <c r="Q21">
-        <v>335.07716254890443</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
+        <v>328.1193865278937</v>
+      </c>
+      <c r="R21">
+        <v>333.1811658139911</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>300.59787546283428</v>
+        <v>301.4430905629401</v>
       </c>
       <c r="C22">
-        <v>310.84257823947758</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D22">
-        <v>289.90685260928348</v>
+        <v>310.9205922439641</v>
       </c>
       <c r="E22">
-        <v>286.16310591950571</v>
+        <v>290.4230597375012</v>
       </c>
       <c r="F22">
-        <v>284.19249825067197</v>
+        <v>286.694491119949</v>
       </c>
       <c r="G22">
-        <v>290.58342335041169</v>
+        <v>284.5448982321572</v>
       </c>
       <c r="H22">
-        <v>285.78917319077323</v>
+        <v>290.9678094135815</v>
       </c>
       <c r="I22">
-        <v>297.5055544100822</v>
+        <v>285.5248954539983</v>
       </c>
       <c r="J22">
-        <v>299.19019126529548</v>
+        <v>297.4989124573244</v>
       </c>
       <c r="K22">
-        <v>297.12398356638829</v>
+        <v>300.2532933425022</v>
       </c>
       <c r="L22">
-        <v>301.90126142905672</v>
+        <v>298.6222396933777</v>
       </c>
       <c r="M22">
-        <v>309.68118715595142</v>
+        <v>303.5713292831261</v>
       </c>
       <c r="N22">
-        <v>312.34943376596169</v>
+        <v>311.1386427267325</v>
       </c>
       <c r="O22">
-        <v>319.84730108257088</v>
+        <v>313.3841592837744</v>
       </c>
       <c r="P22">
-        <v>329.84174952960672</v>
+        <v>322.4778955864629</v>
       </c>
       <c r="Q22">
-        <v>332.17093161183448</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
+        <v>331.694326420329</v>
+      </c>
+      <c r="R22">
+        <v>333.6251024214693</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>294.13216213510191</v>
+        <v>292.5069524514956</v>
       </c>
       <c r="C23">
-        <v>290.20989894610068</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D23">
-        <v>309.77042660286168</v>
+        <v>290.1049238717687</v>
       </c>
       <c r="E23">
-        <v>299.98555016588728</v>
+        <v>309.2642773675329</v>
       </c>
       <c r="F23">
-        <v>289.98916429943932</v>
+        <v>298.1513480537516</v>
       </c>
       <c r="G23">
-        <v>289.4929695274526</v>
+        <v>286.8349352137949</v>
       </c>
       <c r="H23">
-        <v>285.88212422064811</v>
+        <v>287.5976801360117</v>
       </c>
       <c r="I23">
-        <v>291.30688527607663</v>
+        <v>284.9736810083996</v>
       </c>
       <c r="J23">
-        <v>293.94872711338257</v>
+        <v>291.3696734391966</v>
       </c>
       <c r="K23">
-        <v>302.48725463919089</v>
+        <v>293.9776441000292</v>
       </c>
       <c r="L23">
-        <v>307.28659474764521</v>
+        <v>301.9096269773944</v>
       </c>
       <c r="M23">
-        <v>313.07478972426088</v>
+        <v>304.6042586547648</v>
       </c>
       <c r="N23">
-        <v>312.10007512736388</v>
+        <v>310.5489967962191</v>
       </c>
       <c r="O23">
-        <v>313.13319074358532</v>
+        <v>309.9596541942655</v>
       </c>
       <c r="P23">
-        <v>315.47138388854057</v>
+        <v>311.8628491949858</v>
       </c>
       <c r="Q23">
-        <v>321.07793352080279</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
+        <v>315.4805563870805</v>
+      </c>
+      <c r="R23">
+        <v>322.4122799191392</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>367.59792616506019</v>
+        <v>298.1461731977697</v>
       </c>
       <c r="C24">
-        <v>367.59792616506019</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D24">
-        <v>391.77676727696388</v>
+        <v>293.5298577179836</v>
       </c>
       <c r="E24">
-        <v>394.52008307189919</v>
+        <v>284.212337184566</v>
       </c>
       <c r="F24">
-        <v>402.38011161327432</v>
+        <v>278.4232867393031</v>
       </c>
       <c r="G24">
-        <v>428.80647472231209</v>
+        <v>272.5479059306136</v>
       </c>
       <c r="H24">
-        <v>428.32830913642391</v>
+        <v>282.4803633014614</v>
       </c>
       <c r="I24">
-        <v>426.42352433446081</v>
+        <v>290.730947641223</v>
       </c>
       <c r="J24">
-        <v>434.67041400449921</v>
+        <v>297.4688246658687</v>
       </c>
       <c r="K24">
-        <v>445.0125123703902</v>
+        <v>274.3843438105584</v>
       </c>
       <c r="L24">
-        <v>467.24101049290391</v>
+        <v>264.2454705611531</v>
       </c>
       <c r="M24">
-        <v>465.89456524795969</v>
+        <v>269.2671558854499</v>
       </c>
       <c r="N24">
-        <v>459.10687380298941</v>
+        <v>262.0960645579032</v>
       </c>
       <c r="O24">
-        <v>451.08287401146691</v>
+        <v>272.6767351206993</v>
       </c>
       <c r="P24">
-        <v>444.62814832464198</v>
+        <v>273.3278695766194</v>
       </c>
       <c r="Q24">
-        <v>442.5023476603144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
+        <v>278.5056870919195</v>
+      </c>
+      <c r="R24">
+        <v>286.2482441750947</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>370.49894939188442</v>
+        <v>289.3057836214908</v>
       </c>
       <c r="C25">
-        <v>370.49894939188442</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D25">
-        <v>391.03466075447938</v>
+        <v>293.5612725088462</v>
       </c>
       <c r="E25">
-        <v>399.58981612124381</v>
+        <v>283.2859556359767</v>
       </c>
       <c r="F25">
-        <v>426.7849697458762</v>
+        <v>276.6747310597383</v>
       </c>
       <c r="G25">
-        <v>428.32456905005267</v>
+        <v>270.6326394842804</v>
       </c>
       <c r="H25">
-        <v>444.57777571140628</v>
+        <v>283.9455944317675</v>
       </c>
       <c r="I25">
-        <v>474.77188425568409</v>
+        <v>281.7307759117657</v>
       </c>
       <c r="J25">
-        <v>488.75704931085409</v>
+        <v>285.0020989773684</v>
       </c>
       <c r="K25">
-        <v>480.16878126491957</v>
+        <v>270.8601067231434</v>
       </c>
       <c r="L25">
-        <v>485.56187382006698</v>
+        <v>259.1257717684367</v>
       </c>
       <c r="M25">
-        <v>493.98455341905441</v>
+        <v>256.737281901244</v>
       </c>
       <c r="N25">
-        <v>507.58267278630319</v>
+        <v>252.4644284719498</v>
       </c>
       <c r="O25">
-        <v>518.53998400103228</v>
+        <v>249.5022382799229</v>
       </c>
       <c r="P25">
-        <v>513.37575230360426</v>
+        <v>253.8356840762697</v>
       </c>
       <c r="Q25">
-        <v>511.78490816538499</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>41</v>
+        <v>258.1764580900677</v>
+      </c>
+      <c r="R25">
+        <v>266.2876431776841</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>367.21660207750142</v>
+        <v>296.1411051328965</v>
       </c>
       <c r="C26">
-        <v>367.21660207750142</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D26">
-        <v>377.60322205778982</v>
+        <v>290.5902680785952</v>
       </c>
       <c r="E26">
-        <v>378.63186049748037</v>
+        <v>285.391335907129</v>
       </c>
       <c r="F26">
-        <v>397.73686988504448</v>
+        <v>282.3467116104118</v>
       </c>
       <c r="G26">
-        <v>407.28812853023197</v>
+        <v>277.431351245209</v>
       </c>
       <c r="H26">
-        <v>398.78203741111088</v>
+        <v>288.2113534063377</v>
       </c>
       <c r="I26">
-        <v>391.73734504538271</v>
+        <v>290.7611226673026</v>
       </c>
       <c r="J26">
-        <v>394.90196274149793</v>
+        <v>290.4170442392019</v>
       </c>
       <c r="K26">
-        <v>394.76570302101197</v>
+        <v>272.1037569857223</v>
       </c>
       <c r="L26">
-        <v>381.96676810225608</v>
+        <v>258.0522224848572</v>
       </c>
       <c r="M26">
-        <v>412.95057523951073</v>
+        <v>264.8420684414093</v>
       </c>
       <c r="N26">
-        <v>428.25659622443908</v>
+        <v>259.707181317751</v>
       </c>
       <c r="O26">
-        <v>426.03692628289502</v>
+        <v>258.5679183370522</v>
       </c>
       <c r="P26">
-        <v>434.86402308747802</v>
+        <v>260.3697856082907</v>
       </c>
       <c r="Q26">
-        <v>439.15852291428303</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
+        <v>266.0081423654493</v>
+      </c>
+      <c r="R26">
+        <v>276.8857089916647</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>367.74880047860188</v>
+        <v>288.4695343034389</v>
       </c>
       <c r="C27">
-        <v>367.2376550225452</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D27">
-        <v>372.17674814277132</v>
+        <v>290.6482740627322</v>
       </c>
       <c r="E27">
-        <v>414.49271426865528</v>
+        <v>284.927671529297</v>
       </c>
       <c r="F27">
-        <v>403.42846260038061</v>
+        <v>281.2244331779069</v>
       </c>
       <c r="G27">
-        <v>390.66513719276702</v>
+        <v>276.7392192367802</v>
       </c>
       <c r="H27">
-        <v>393.29396104893777</v>
+        <v>285.2749204809075</v>
       </c>
       <c r="I27">
-        <v>392.43388205340858</v>
+        <v>288.0761893954642</v>
       </c>
       <c r="J27">
-        <v>382.22352058188812</v>
+        <v>290.1173932648222</v>
       </c>
       <c r="K27">
-        <v>397.4821838318714</v>
+        <v>276.3151618012947</v>
       </c>
       <c r="L27">
-        <v>410.82282559175252</v>
+        <v>261.326083917319</v>
       </c>
       <c r="M27">
-        <v>418.83019570018718</v>
+        <v>261.632128516096</v>
       </c>
       <c r="N27">
-        <v>426.74605451800431</v>
+        <v>256.7826586044708</v>
       </c>
       <c r="O27">
-        <v>426.6034389066906</v>
+        <v>251.6999231660334</v>
       </c>
       <c r="P27">
-        <v>440.04939875462708</v>
+        <v>245.9641132822293</v>
       </c>
       <c r="Q27">
-        <v>449.58586987163352</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
+        <v>251.8361775263642</v>
+      </c>
+      <c r="R27">
+        <v>245.7116005918586</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>297.2390987840202</v>
+        <v>285.5381151835977</v>
       </c>
       <c r="C28">
-        <v>293.35138415593161</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D28">
-        <v>283.66604400032469</v>
+        <v>293.5646900799806</v>
       </c>
       <c r="E28">
-        <v>277.68429930104247</v>
-      </c>
-      <c r="F28" s="2">
-        <v>272.00240780405261</v>
+        <v>283.5239101100956</v>
+      </c>
+      <c r="F28">
+        <v>277.1020661029508</v>
       </c>
       <c r="G28">
-        <v>281.71361986527558</v>
+        <v>270.8533916796767</v>
       </c>
       <c r="H28">
-        <v>290.53148736867672</v>
+        <v>283.2181533446347</v>
       </c>
       <c r="I28">
-        <v>298.33351004678428</v>
+        <v>282.806592633176</v>
       </c>
       <c r="J28">
-        <v>276.28246254223183</v>
+        <v>285.7266608447065</v>
       </c>
       <c r="K28">
-        <v>264.56522954662319</v>
+        <v>274.6553542081596</v>
       </c>
       <c r="L28">
-        <v>269.27824574277668</v>
+        <v>263.924710380849</v>
       </c>
       <c r="M28">
-        <v>262.17802207440729</v>
+        <v>254.3832378122754</v>
       </c>
       <c r="N28">
-        <v>273.13194241658942</v>
+        <v>250.2919128272632</v>
       </c>
       <c r="O28">
-        <v>273.80030252492571</v>
+        <v>245.2758273660485</v>
       </c>
       <c r="P28">
-        <v>278.86211279658079</v>
+        <v>249.7489883634564</v>
       </c>
       <c r="Q28">
-        <v>286.05979289396811</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>44</v>
+        <v>247.2877255750123</v>
+      </c>
+      <c r="R28">
+        <v>251.7420973845361</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>288.92698756469667</v>
+        <v>287.7840786894776</v>
       </c>
       <c r="C29">
-        <v>293.78087795404178</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D29">
-        <v>284.07623899071359</v>
+        <v>294.1394642671673</v>
       </c>
       <c r="E29">
-        <v>277.38050757786942</v>
-      </c>
-      <c r="F29" s="2">
-        <v>270.85095308827141</v>
+        <v>284.7371000146058</v>
+      </c>
+      <c r="F29">
+        <v>278.248894692402</v>
       </c>
       <c r="G29">
-        <v>285.29526450463419</v>
+        <v>271.6757821593879</v>
       </c>
       <c r="H29">
-        <v>284.09389416554012</v>
+        <v>284.0725744189418</v>
       </c>
       <c r="I29">
-        <v>286.50935023271722</v>
+        <v>282.7652494232844</v>
       </c>
       <c r="J29">
-        <v>271.67856896837509</v>
+        <v>286.3856950830015</v>
       </c>
       <c r="K29">
-        <v>260.28374287772277</v>
+        <v>276.0243057717624</v>
       </c>
       <c r="L29">
-        <v>256.77896811223508</v>
+        <v>265.8201220288984</v>
       </c>
       <c r="M29">
-        <v>253.1466969242656</v>
+        <v>255.6475241512881</v>
       </c>
       <c r="N29">
-        <v>251.17156977576309</v>
+        <v>249.5493978727001</v>
       </c>
       <c r="O29">
-        <v>254.90550832871591</v>
+        <v>244.6700588368333</v>
       </c>
       <c r="P29">
-        <v>260.157180056968</v>
+        <v>249.2273093265439</v>
       </c>
       <c r="Q29">
-        <v>267.74290514570919</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>45</v>
+        <v>247.5036052223644</v>
+      </c>
+      <c r="R29">
+        <v>253.0699357339971</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>296.85788858999359</v>
+        <v>286.3376099386358</v>
       </c>
       <c r="C30">
-        <v>290.89677040945202</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D30">
-        <v>285.4637185486381</v>
+        <v>293.4525172341711</v>
       </c>
       <c r="E30">
-        <v>282.48979830679809</v>
+        <v>283.3945066575019</v>
       </c>
       <c r="F30">
-        <v>277.82710779198851</v>
+        <v>276.8426743384716</v>
       </c>
       <c r="G30">
-        <v>288.01550846900852</v>
+        <v>270.3586414163655</v>
       </c>
       <c r="H30">
-        <v>291.04144318707762</v>
+        <v>283.4745023246229</v>
       </c>
       <c r="I30">
-        <v>291.14127595309122</v>
+        <v>282.6446425715163</v>
       </c>
       <c r="J30">
-        <v>272.88461001677081</v>
-      </c>
-      <c r="K30" s="2">
-        <v>259.27829468895078</v>
+        <v>285.0630566036523</v>
+      </c>
+      <c r="K30">
+        <v>275.7895058937659</v>
       </c>
       <c r="L30">
-        <v>265.98729764431579</v>
+        <v>264.5595230613413</v>
       </c>
       <c r="M30">
-        <v>260.59673584072971</v>
+        <v>257.8438692031094</v>
       </c>
       <c r="N30">
-        <v>259.69990823032111</v>
+        <v>250.3950614403974</v>
       </c>
       <c r="O30">
-        <v>261.31674428536769</v>
+        <v>245.6688718340983</v>
       </c>
       <c r="P30">
-        <v>268.40140580613343</v>
+        <v>251.2920109492034</v>
       </c>
       <c r="Q30">
-        <v>279.45063231403878</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>46</v>
+        <v>249.1784126720464</v>
+      </c>
+      <c r="R30">
+        <v>254.8790416591944</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>289.4677454873227</v>
+        <v>283.1355319306639</v>
       </c>
       <c r="C31">
-        <v>290.44250918273508</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D31">
-        <v>285.22951093124021</v>
+        <v>293.4226139336308</v>
       </c>
       <c r="E31">
-        <v>283.14418912491368</v>
+        <v>283.2885763307622</v>
       </c>
       <c r="F31">
-        <v>276.49275101432642</v>
+        <v>276.1375911535785</v>
       </c>
       <c r="G31">
-        <v>287.13437248751541</v>
+        <v>269.821568661388</v>
       </c>
       <c r="H31">
-        <v>290.58785012061162</v>
+        <v>281.3007037564158</v>
       </c>
       <c r="I31">
-        <v>292.50776470970959</v>
+        <v>281.7700832791958</v>
       </c>
       <c r="J31">
-        <v>276.27772553239669</v>
-      </c>
-      <c r="K31" s="2">
-        <v>260.74816970436967</v>
+        <v>284.8139100212811</v>
+      </c>
+      <c r="K31">
+        <v>275.8720625916914</v>
       </c>
       <c r="L31">
-        <v>261.85783923468261</v>
+        <v>264.4748895588189</v>
       </c>
       <c r="M31">
-        <v>257.61206338274059</v>
+        <v>257.140690910069</v>
       </c>
       <c r="N31">
-        <v>253.6728550262475</v>
+        <v>249.7026173804265</v>
       </c>
       <c r="O31">
-        <v>245.91597479606901</v>
+        <v>244.5558685910529</v>
       </c>
       <c r="P31">
-        <v>251.801802347912</v>
+        <v>248.9648120021938</v>
       </c>
       <c r="Q31">
-        <v>245.42025338348529</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>47</v>
+        <v>246.0060165626659</v>
+      </c>
+      <c r="R31">
+        <v>250.6214493351097</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>284.48701338540559</v>
+        <v>287.2591429919568</v>
       </c>
       <c r="C32">
-        <v>293.49831057800822</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D32">
-        <v>283.85526419644452</v>
+        <v>293.4883374426796</v>
       </c>
       <c r="E32">
-        <v>277.64931980155689</v>
-      </c>
-      <c r="F32" s="2">
-        <v>271.11586170942678</v>
+        <v>283.3233573155503</v>
+      </c>
+      <c r="F32">
+        <v>276.546589603816</v>
       </c>
       <c r="G32">
-        <v>283.37992064120789</v>
+        <v>270.2422157078082</v>
       </c>
       <c r="H32">
-        <v>282.50724589406587</v>
+        <v>283.1893504772772</v>
       </c>
       <c r="I32">
-        <v>285.94667793228399</v>
+        <v>282.4004947831561</v>
       </c>
       <c r="J32">
-        <v>276.49308102417842</v>
+        <v>287.0559967983926</v>
       </c>
       <c r="K32">
-        <v>266.11885688786492</v>
+        <v>274.8077456853738</v>
       </c>
       <c r="L32">
-        <v>257.05974183445772</v>
+        <v>266.1776186792137</v>
       </c>
       <c r="M32">
-        <v>251.8810375859251</v>
+        <v>258.9460993581968</v>
       </c>
       <c r="N32">
-        <v>246.49981663620139</v>
+        <v>254.3284535124019</v>
       </c>
       <c r="O32">
-        <v>250.60546431904601</v>
+        <v>249.5878230549052</v>
       </c>
       <c r="P32">
-        <v>248.29789926964619</v>
+        <v>254.1531504313198</v>
       </c>
       <c r="Q32">
-        <v>253.708472716382</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>48</v>
+        <v>251.891520534394</v>
+      </c>
+      <c r="R32">
+        <v>258.7140126098685</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>286.23187772999052</v>
+        <v>287.6933282099749</v>
       </c>
       <c r="C33">
-        <v>293.87637697878432</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D33">
-        <v>284.16496696426032</v>
+        <v>294.5674845402374</v>
       </c>
       <c r="E33">
-        <v>277.60131160060939</v>
-      </c>
-      <c r="F33" s="2">
-        <v>270.91792463423292</v>
+        <v>284.8399734492628</v>
+      </c>
+      <c r="F33">
+        <v>277.5868257035895</v>
       </c>
       <c r="G33">
-        <v>282.98131695451389</v>
+        <v>271.4173268248233</v>
       </c>
       <c r="H33">
-        <v>281.83565246365691</v>
+        <v>284.7409327628805</v>
       </c>
       <c r="I33">
-        <v>284.78235482779911</v>
+        <v>284.4887311958425</v>
       </c>
       <c r="J33">
-        <v>274.68181013142868</v>
+        <v>286.3113520858899</v>
       </c>
       <c r="K33">
-        <v>265.25589993706382</v>
+        <v>273.9803817151432</v>
       </c>
       <c r="L33">
-        <v>255.77732770792511</v>
+        <v>265.2400062242565</v>
       </c>
       <c r="M33">
-        <v>249.3197975635874</v>
+        <v>256.8916346140107</v>
       </c>
       <c r="N33">
-        <v>244.02448418337161</v>
+        <v>251.2706647947898</v>
       </c>
       <c r="O33">
-        <v>249.2398538965883</v>
+        <v>246.7870370308823</v>
       </c>
       <c r="P33">
-        <v>246.5820591273133</v>
+        <v>249.7376156875609</v>
       </c>
       <c r="Q33">
-        <v>253.20342980564021</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>49</v>
+        <v>248.7804970850502</v>
+      </c>
+      <c r="R33">
+        <v>255.5992138280963</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>285.29636535847749</v>
+        <v>285.7433840050828</v>
       </c>
       <c r="C34">
-        <v>292.92331376180482</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D34">
-        <v>282.99337858912509</v>
+        <v>294.0717963420861</v>
       </c>
       <c r="E34">
-        <v>276.18969004821491</v>
-      </c>
-      <c r="F34" s="2">
-        <v>270.27463190154651</v>
+        <v>283.841193781971</v>
+      </c>
+      <c r="F34">
+        <v>277.616737502185</v>
       </c>
       <c r="G34">
-        <v>283.28319036402672</v>
+        <v>271.1849284150337</v>
       </c>
       <c r="H34">
-        <v>282.14491237028562</v>
+        <v>282.432694842451</v>
       </c>
       <c r="I34">
-        <v>285.54488188673128</v>
+        <v>281.3097521466275</v>
       </c>
       <c r="J34">
-        <v>275.68954682166537</v>
+        <v>283.4768575918434</v>
       </c>
       <c r="K34">
-        <v>264.66825092906618</v>
+        <v>274.3305714906093</v>
       </c>
       <c r="L34">
-        <v>255.98823911695641</v>
+        <v>265.1913550746661</v>
       </c>
       <c r="M34">
-        <v>249.79019648103201</v>
+        <v>258.3085299537049</v>
       </c>
       <c r="N34">
-        <v>244.4727473090993</v>
+        <v>253.1958619231856</v>
       </c>
       <c r="O34">
-        <v>248.81706367851879</v>
+        <v>248.1107518403616</v>
       </c>
       <c r="P34">
-        <v>247.148099311777</v>
+        <v>251.9697015149063</v>
       </c>
       <c r="Q34">
-        <v>252.36847352664509</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>50</v>
+        <v>249.7811272755852</v>
+      </c>
+      <c r="R34">
+        <v>258.756659446486</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>287.2116877410279</v>
+        <v>285.5455729790364</v>
       </c>
       <c r="C35">
-        <v>294.31362065251471</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D35">
-        <v>284.4386205398103</v>
+        <v>293.9033882680619</v>
       </c>
       <c r="E35">
-        <v>278.23522239023771</v>
-      </c>
-      <c r="F35" s="2">
-        <v>271.56261709272121</v>
+        <v>283.9122135812066</v>
+      </c>
+      <c r="F35">
+        <v>277.1036033515492</v>
       </c>
       <c r="G35">
-        <v>284.39490671732381</v>
+        <v>270.4855468820286</v>
       </c>
       <c r="H35">
-        <v>284.98139955198337</v>
+        <v>281.4985124953923</v>
       </c>
       <c r="I35">
-        <v>288.09087400554591</v>
+        <v>280.2805837803867</v>
       </c>
       <c r="J35">
-        <v>277.7188911554075</v>
-      </c>
-      <c r="K35" s="3">
-        <v>269.01756108406289</v>
+        <v>283.8679896394374</v>
+      </c>
+      <c r="K35">
+        <v>273.9269318995125</v>
       </c>
       <c r="L35">
-        <v>260.03384537492838</v>
+        <v>263.4780652471696</v>
       </c>
       <c r="M35">
-        <v>252.9293421163496</v>
+        <v>258.5955873563252</v>
       </c>
       <c r="N35">
-        <v>247.57456965226291</v>
+        <v>250.7478980604618</v>
       </c>
       <c r="O35">
-        <v>252.4991204973287</v>
+        <v>245.6653407410358</v>
       </c>
       <c r="P35">
-        <v>250.23029337585649</v>
+        <v>247.7125079687578</v>
       </c>
       <c r="Q35">
-        <v>255.70754683623019</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>51</v>
+        <v>246.2131719672372</v>
+      </c>
+      <c r="R35">
+        <v>253.3463644594787</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>286.38972736465712</v>
+        <v>286.2524606144232</v>
       </c>
       <c r="C36">
-        <v>293.05820501819773</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D36">
-        <v>282.94503478820877</v>
+        <v>293.6702842399119</v>
       </c>
       <c r="E36">
-        <v>276.26442504689328</v>
+        <v>283.3167792656376</v>
       </c>
       <c r="F36">
-        <v>269.91790075488183</v>
+        <v>276.4292862089247</v>
       </c>
       <c r="G36">
-        <v>282.34880167429839</v>
+        <v>269.9266020994716</v>
       </c>
       <c r="H36">
-        <v>281.39392238789679</v>
+        <v>281.5465267305629</v>
       </c>
       <c r="I36">
-        <v>284.1176546757963</v>
+        <v>280.40058379927</v>
       </c>
       <c r="J36">
-        <v>273.62966378326792</v>
-      </c>
-      <c r="K36" s="2">
-        <v>264.05733795334203</v>
+        <v>283.7351842157659</v>
+      </c>
+      <c r="K36">
+        <v>275.1932683777868</v>
       </c>
       <c r="L36">
-        <v>258.13678974861728</v>
+        <v>264.107107416784</v>
       </c>
       <c r="M36">
-        <v>251.83759241646939</v>
+        <v>257.4338865042609</v>
       </c>
       <c r="N36">
-        <v>248.2065906746196</v>
+        <v>250.054514487413</v>
       </c>
       <c r="O36">
-        <v>252.94959142383351</v>
+        <v>245.1846198546083</v>
       </c>
       <c r="P36">
-        <v>250.20091679780359</v>
+        <v>248.4670416933339</v>
       </c>
       <c r="Q36">
-        <v>256.26485131954462</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>52</v>
+        <v>246.2982710936761</v>
+      </c>
+      <c r="R36">
+        <v>253.4544617739557</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>287.93296104464372</v>
+        <v>291.8165924404337</v>
       </c>
       <c r="C37">
-        <v>293.95035549869471</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D37">
-        <v>284.83566965637732</v>
+        <v>289.5171855845089</v>
       </c>
       <c r="E37">
-        <v>278.79755960330402</v>
-      </c>
-      <c r="F37" s="2">
-        <v>271.84638424954898</v>
+        <v>280.4890028707156</v>
+      </c>
+      <c r="F37">
+        <v>266.3343340717998</v>
       </c>
       <c r="G37">
-        <v>284.89614749656698</v>
+        <v>270.7009251362916</v>
       </c>
       <c r="H37">
-        <v>283.25288547385941</v>
+        <v>283.0405782368509</v>
       </c>
       <c r="I37">
-        <v>286.66946835893469</v>
+        <v>301.2644526521751</v>
       </c>
       <c r="J37">
-        <v>276.20381338897238</v>
+        <v>291.9927890734532</v>
       </c>
       <c r="K37">
-        <v>268.04455564766522</v>
+        <v>290.7714583686403</v>
       </c>
       <c r="L37">
-        <v>259.61486962101691</v>
+        <v>288.5868700667994</v>
       </c>
       <c r="M37">
-        <v>254.28253636115451</v>
+        <v>282.9244000902121</v>
       </c>
       <c r="N37">
-        <v>249.4096110833641</v>
+        <v>291.2714453194151</v>
       </c>
       <c r="O37">
-        <v>252.46727007387321</v>
+        <v>294.0338320762032</v>
       </c>
       <c r="P37">
-        <v>250.08915082653641</v>
+        <v>297.0663279693281</v>
       </c>
       <c r="Q37">
-        <v>257.66712583659148</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>53</v>
+        <v>298.3912502563724</v>
+      </c>
+      <c r="R37">
+        <v>301.103087763338</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>285.04670495583031</v>
+        <v>286.2751403338862</v>
       </c>
       <c r="C38">
-        <v>294.44864121510619</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D38">
-        <v>284.06501495805833</v>
+        <v>289.1224601659265</v>
       </c>
       <c r="E38">
-        <v>277.35006383575819</v>
+        <v>279.3817685364556</v>
       </c>
       <c r="F38">
-        <v>270.7852793864991</v>
+        <v>267.6795886153393</v>
       </c>
       <c r="G38">
-        <v>282.12586215055461</v>
+        <v>274.1218022930004</v>
       </c>
       <c r="H38">
-        <v>281.12238287194589</v>
+        <v>284.9645758382114</v>
       </c>
       <c r="I38">
-        <v>284.69292697842383</v>
+        <v>277.1519055045316</v>
       </c>
       <c r="J38">
-        <v>273.89265523671901</v>
-      </c>
-      <c r="K38" s="2">
-        <v>262.08128129010782</v>
+        <v>269.7298893655895</v>
+      </c>
+      <c r="K38">
+        <v>267.8026659828724</v>
       </c>
       <c r="L38">
-        <v>257.35619621211271</v>
+        <v>266.8781148562053</v>
       </c>
       <c r="M38">
-        <v>251.5529795489702</v>
+        <v>258.6869998146881</v>
       </c>
       <c r="N38">
-        <v>246.68323508284681</v>
+        <v>259.9287907321535</v>
       </c>
       <c r="O38">
-        <v>248.78986326593119</v>
+        <v>250.2701269400472</v>
       </c>
       <c r="P38">
-        <v>246.56651767650101</v>
+        <v>245.031500926885</v>
       </c>
       <c r="Q38">
-        <v>254.01837661321059</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
+        <v>241.509364944224</v>
+      </c>
+      <c r="R38">
+        <v>245.6183935118868</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>286.26462153100158</v>
+        <v>283.4248955461496</v>
       </c>
       <c r="C39">
-        <v>293.51809324516682</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D39">
-        <v>283.16325224742877</v>
+        <v>288.8404052829112</v>
       </c>
       <c r="E39">
-        <v>276.67493398738901</v>
+        <v>277.3508275681997</v>
       </c>
       <c r="F39">
-        <v>270.28983348449378</v>
+        <v>266.733358931527</v>
       </c>
       <c r="G39">
-        <v>281.4091859610773</v>
+        <v>272.3180444507157</v>
       </c>
       <c r="H39">
-        <v>281.1722790716293</v>
+        <v>282.8572662052924</v>
       </c>
       <c r="I39">
-        <v>283.9249194558447</v>
+        <v>271.5690061209463</v>
       </c>
       <c r="J39">
-        <v>273.19067651747969</v>
-      </c>
-      <c r="K39" s="2">
-        <v>264.08221475465399</v>
+        <v>263.07493351825</v>
+      </c>
+      <c r="K39">
+        <v>264.7851804657637</v>
       </c>
       <c r="L39">
-        <v>257.57899459572451</v>
+        <v>259.9686219750007</v>
       </c>
       <c r="M39">
-        <v>251.66576945867979</v>
+        <v>253.7132754855237</v>
       </c>
       <c r="N39">
-        <v>246.14673029080731</v>
+        <v>255.8279376932793</v>
       </c>
       <c r="O39">
-        <v>248.9814526745723</v>
+        <v>246.6993219383459</v>
       </c>
       <c r="P39">
-        <v>246.92039066594069</v>
+        <v>245.6338410834002</v>
       </c>
       <c r="Q39">
-        <v>254.49932991614139</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>55</v>
+        <v>244.392782247451</v>
+      </c>
+      <c r="R39">
+        <v>247.7131172258841</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>285.24202014968421</v>
+        <v>293.2338012020883</v>
       </c>
       <c r="C40">
-        <v>293.792862665683</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D40">
-        <v>283.67497558401232</v>
+        <v>293.9879902036978</v>
       </c>
       <c r="E40">
-        <v>276.21535686333362</v>
+        <v>292.0574127916452</v>
       </c>
       <c r="F40">
-        <v>269.77090825255033</v>
+        <v>277.3800589734267</v>
       </c>
       <c r="G40">
-        <v>282.23284530102791</v>
+        <v>274.6921660267961</v>
       </c>
       <c r="H40">
-        <v>281.59010047208221</v>
+        <v>274.974098153612</v>
       </c>
       <c r="I40">
-        <v>283.82246220454527</v>
+        <v>267.2053300184186</v>
       </c>
       <c r="J40">
-        <v>274.69832378134879</v>
-      </c>
-      <c r="K40" s="2">
-        <v>265.17184767936698</v>
+        <v>268.4909985564289</v>
+      </c>
+      <c r="K40">
+        <v>269.3300448961782</v>
       </c>
       <c r="L40">
-        <v>259.82195954817439</v>
+        <v>272.9672909796543</v>
       </c>
       <c r="M40">
-        <v>251.3600517204265</v>
+        <v>277.3759368633316</v>
       </c>
       <c r="N40">
-        <v>245.9799471717337</v>
+        <v>274.6937208850709</v>
       </c>
       <c r="O40">
-        <v>248.91737075021919</v>
+        <v>276.4660355759705</v>
       </c>
       <c r="P40">
-        <v>245.63091911513021</v>
+        <v>277.5393764334949</v>
       </c>
       <c r="Q40">
-        <v>253.85558299315619</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
+        <v>280.6362866053344</v>
+      </c>
+      <c r="R40">
+        <v>290.3155150736949</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>291.48121713349258</v>
+        <v>294.004843475809</v>
       </c>
       <c r="C41">
-        <v>289.27872622515872</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D41">
-        <v>279.1087556823324</v>
-      </c>
-      <c r="E41" s="2">
-        <v>265.53033575018128</v>
+        <v>293.6586723344533</v>
+      </c>
+      <c r="E41">
+        <v>285.1642007302843</v>
       </c>
       <c r="F41">
-        <v>270.23317635201062</v>
+        <v>284.6706445035525</v>
       </c>
       <c r="G41">
-        <v>284.98222046767643</v>
+        <v>290.7948183537326</v>
       </c>
       <c r="H41">
-        <v>301.90130142516949</v>
+        <v>296.5020095716226</v>
       </c>
       <c r="I41">
-        <v>294.51989404600732</v>
+        <v>302.8253897892305</v>
       </c>
       <c r="J41">
-        <v>292.55014757242299</v>
+        <v>304.8730437455578</v>
       </c>
       <c r="K41">
-        <v>290.94952049269278</v>
+        <v>305.9301566458258</v>
       </c>
       <c r="L41">
-        <v>285.69127903249932</v>
+        <v>308.2966243749893</v>
       </c>
       <c r="M41">
-        <v>293.48001275202643</v>
+        <v>323.1959699737365</v>
       </c>
       <c r="N41">
-        <v>295.52766078271048</v>
+        <v>330.1430606638104</v>
       </c>
       <c r="O41">
-        <v>298.18098095920681</v>
+        <v>334.7530302949683</v>
       </c>
       <c r="P41">
-        <v>299.15028271512551</v>
+        <v>343.0175714731421</v>
       </c>
       <c r="Q41">
-        <v>302.15638151362378</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>57</v>
+        <v>347.3818924728445</v>
+      </c>
+      <c r="R41">
+        <v>343.3496132300771</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>285.78723450160169</v>
+        <v>307.7152552101161</v>
       </c>
       <c r="C42">
-        <v>288.73028355091401</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D42">
-        <v>279.39697160686973</v>
-      </c>
-      <c r="E42" s="2">
-        <v>267.22406903301771</v>
+        <v>313.206239592523</v>
+      </c>
+      <c r="E42">
+        <v>290.4365670843181</v>
       </c>
       <c r="F42">
-        <v>274.19673838762122</v>
+        <v>290.2358183045811</v>
       </c>
       <c r="G42">
-        <v>286.04965523268203</v>
+        <v>297.9153425820528</v>
       </c>
       <c r="H42">
-        <v>278.07846173940868</v>
+        <v>309.875210284465</v>
       </c>
       <c r="I42">
-        <v>270.23469430111112</v>
+        <v>306.5009582287213</v>
       </c>
       <c r="J42">
-        <v>267.0606365852239</v>
+        <v>300.5485729322136</v>
       </c>
       <c r="K42">
-        <v>267.98227838776432</v>
+        <v>303.680062929373</v>
       </c>
       <c r="L42">
-        <v>260.11743242839322</v>
+        <v>319.9066160386357</v>
       </c>
       <c r="M42">
-        <v>259.46508437790538</v>
+        <v>326.4513897207902</v>
       </c>
       <c r="N42">
-        <v>250.53071738204159</v>
+        <v>329.3387847624497</v>
       </c>
       <c r="O42">
-        <v>244.26959943111351</v>
+        <v>337.6451695399598</v>
       </c>
       <c r="P42">
-        <v>240.50347815080701</v>
+        <v>343.745186046682</v>
       </c>
       <c r="Q42">
-        <v>244.87846777862879</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>58</v>
+        <v>342.0563987959487</v>
+      </c>
+      <c r="R42">
+        <v>339.1603333264485</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>283.55789281365389</v>
+        <v>297.43456735981</v>
       </c>
       <c r="C43">
-        <v>288.65421160357471</v>
+        <v>373.1884614245382</v>
       </c>
       <c r="D43">
-        <v>279.97514953765051</v>
-      </c>
-      <c r="E43" s="2">
-        <v>266.89589762166952</v>
+        <v>290.2935248577414</v>
+      </c>
+      <c r="E43">
+        <v>288.6074637880996</v>
       </c>
       <c r="F43">
-        <v>273.80629019037423</v>
+        <v>290.7364195435498</v>
       </c>
       <c r="G43">
-        <v>285.01022423566849</v>
+        <v>291.7528629576206</v>
       </c>
       <c r="H43">
-        <v>273.96964885097691</v>
+        <v>297.614611090774</v>
       </c>
       <c r="I43">
-        <v>264.45015280462019</v>
+        <v>297.1511274745466</v>
       </c>
       <c r="J43">
-        <v>267.15443555999428</v>
+        <v>294.4463823654033</v>
       </c>
       <c r="K43">
-        <v>262.61927782724689</v>
+        <v>292.9590489885146</v>
       </c>
       <c r="L43">
-        <v>254.85823423082539</v>
+        <v>307.8281882112698</v>
       </c>
       <c r="M43">
-        <v>256.93216747853683</v>
+        <v>306.7406047541027</v>
       </c>
       <c r="N43">
-        <v>246.0875039338865</v>
+        <v>309.5293172698279</v>
       </c>
       <c r="O43">
-        <v>244.53573962491711</v>
+        <v>313.2325951694965</v>
       </c>
       <c r="P43">
-        <v>241.34454539754611</v>
+        <v>312.1155541158948</v>
       </c>
       <c r="Q43">
-        <v>243.78994954701719</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>59</v>
-      </c>
-      <c r="B44">
-        <v>292.00693442135707</v>
-      </c>
-      <c r="C44">
-        <v>293.68557819237628</v>
-      </c>
-      <c r="D44">
-        <v>291.88371731157571</v>
-      </c>
-      <c r="E44">
-        <v>276.67777467270491</v>
-      </c>
-      <c r="F44">
-        <v>274.71818483850541</v>
-      </c>
-      <c r="G44">
-        <v>275.14609512599878</v>
-      </c>
-      <c r="H44" s="2">
-        <v>267.67833395952749</v>
-      </c>
-      <c r="I44">
-        <v>268.96608551843929</v>
-      </c>
-      <c r="J44">
-        <v>269.88274169577988</v>
-      </c>
-      <c r="K44">
-        <v>272.40640270827453</v>
-      </c>
-      <c r="L44">
-        <v>277.13770555139712</v>
-      </c>
-      <c r="M44">
-        <v>274.20700848607748</v>
-      </c>
-      <c r="N44">
-        <v>275.88204240647752</v>
-      </c>
-      <c r="O44">
-        <v>276.8128143314467</v>
-      </c>
-      <c r="P44">
-        <v>281.26564298541962</v>
-      </c>
-      <c r="Q44">
-        <v>290.75172571663973</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B45">
-        <v>293.91979960306071</v>
-      </c>
-      <c r="C45">
-        <v>293.59342419253738</v>
-      </c>
-      <c r="D45">
-        <v>284.68858830373961</v>
-      </c>
-      <c r="E45">
-        <v>284.20579564162131</v>
-      </c>
-      <c r="F45">
-        <v>289.50120375756961</v>
-      </c>
-      <c r="G45">
-        <v>295.89118558625518</v>
-      </c>
-      <c r="H45">
-        <v>301.82351589942209</v>
-      </c>
-      <c r="I45">
-        <v>303.85257725678269</v>
-      </c>
-      <c r="J45">
-        <v>304.77896998579638</v>
-      </c>
-      <c r="K45">
-        <v>307.54740595001988</v>
-      </c>
-      <c r="L45">
-        <v>321.97005917482312</v>
-      </c>
-      <c r="M45">
-        <v>328.40324697194433</v>
-      </c>
-      <c r="N45">
-        <v>331.11052726105322</v>
-      </c>
-      <c r="O45">
-        <v>339.3720503533649</v>
-      </c>
-      <c r="P45">
-        <v>344.53896763367737</v>
-      </c>
-      <c r="Q45">
-        <v>340.80492748761827</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B46">
-        <v>306.36492568251788</v>
-      </c>
-      <c r="C46">
-        <v>313.0029897320448</v>
-      </c>
-      <c r="D46">
-        <v>290.10866426176392</v>
-      </c>
-      <c r="E46">
-        <v>289.55583732755241</v>
-      </c>
-      <c r="F46">
-        <v>296.91912866346149</v>
-      </c>
-      <c r="G46">
-        <v>308.53892383810108</v>
-      </c>
-      <c r="H46">
-        <v>305.59013479196949</v>
-      </c>
-      <c r="I46">
-        <v>299.60689953106697</v>
-      </c>
-      <c r="J46">
-        <v>302.41522730420547</v>
-      </c>
-      <c r="K46">
-        <v>317.33997904569469</v>
-      </c>
-      <c r="L46">
-        <v>323.95377002189502</v>
-      </c>
-      <c r="M46">
-        <v>327.5735903245187</v>
-      </c>
-      <c r="N46">
-        <v>335.80932142174868</v>
-      </c>
-      <c r="O46">
-        <v>340.94776251127371</v>
-      </c>
-      <c r="P46">
-        <v>338.3315858180369</v>
-      </c>
-      <c r="Q46">
-        <v>335.93416631027537</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47">
-        <v>297.97815841813019</v>
-      </c>
-      <c r="C47">
-        <v>290.1083231237775</v>
-      </c>
-      <c r="D47">
-        <v>288.61612849135059</v>
-      </c>
-      <c r="E47">
-        <v>290.25476912428741</v>
-      </c>
-      <c r="F47">
-        <v>290.92322658912758</v>
-      </c>
-      <c r="G47">
-        <v>296.99728490754421</v>
-      </c>
-      <c r="H47">
-        <v>296.02216054283952</v>
-      </c>
-      <c r="I47">
-        <v>291.94290484950261</v>
-      </c>
-      <c r="J47">
-        <v>291.04993573154741</v>
-      </c>
-      <c r="K47">
-        <v>305.90678025980122</v>
-      </c>
-      <c r="L47">
-        <v>304.81341256310679</v>
-      </c>
-      <c r="M47">
-        <v>307.35129459971682</v>
-      </c>
-      <c r="N47">
-        <v>310.19178751881913</v>
-      </c>
-      <c r="O47">
-        <v>309.2363003919229</v>
-      </c>
-      <c r="P47">
-        <v>310.5886015340285</v>
-      </c>
-      <c r="Q47">
-        <v>312.84961538727879</v>
+        <v>313.4684407551945</v>
+      </c>
+      <c r="R43">
+        <v>315.4789905484319</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:Q47">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>